--- a/context_DB/ETH_context_db.xlsx
+++ b/context_DB/ETH_context_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL20"/>
+  <dimension ref="A1:BL62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1017,68 +1017,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ET0106</t>
+          <t>ET0104</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ET0604</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ET0102;ET0103;ET0106;ET0415;ET0422;ET0604;ET0802</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>72.70360568058959</v>
-      </c>
-      <c r="I4" t="n">
-        <v>26.89260752834676</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.4037867910636499</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>21.08</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P4" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.34</v>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
@@ -1106,20 +1068,68 @@
       <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tigray</t>
+        </is>
+      </c>
+      <c r="AY4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>ET01</t>
+        </is>
+      </c>
       <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>Strategic developments ---- Protests ---- Protests ---- Violence against civilians ---- Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>Headquarters or base established ---- Excessive force against protesters ---- Excessive force against protesters ---- Attack ---- Attack</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>Police Forces of Ethiopia (2018-) Tigray State Police ---- Protesters (Ethiopia) ---- Protesters (Ethiopia) ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-)</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>Kebele Communal Militia (Ethiopia) ---- Amhara Ethnic Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>TPLF: Tigray People's Liberation Front ---- Police Forces of Ethiopia (2018-) Tigray State Police ---- Civilians (Ethiopia) ---- Civilians (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>TPLF: Tigray People's Liberation Front ---- Orthodox Christian Group (Ethiopia); Students (Ethiopia); Teachers (Ethiopia) ---- Orthodox Christian Group (Ethiopia); Students (Ethiopia); Teachers (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>Around 31 May 2024 (as reported), Tigray forces (likely Tigray State police and Kebele militia based on their involvement in the clashes in the area) entered Alamata town and stationed in Mabrat school and Addis Alem school in Alamata (Alamata town, Southern Tigray, Tigray). The town remained under the control of ENDF. Tigray Forces established two checkpoints at unspecified locations near Alamata and started checking the identity of the travelers who passed through these checkpoints. ---- On 9 June 2024, for a second day, thousands of residents of Alamata town protested in Alamata (Southern Tigray, Tigray), against the presence of TPLF forces and the alleged killing of an electricity worker by the TPLF militants (coded separately). The protesters called for their withdrawal from Alamata and its surrounding areas. The TPLF forces who were camped in a nearby school opened fire and killed a protester and wounded another. ---- On 1 October 2024, ethnic Amhara residents and students staged a protest against the start of students' registration based on Tigray regional state's curriculum, around Midre Genet Elementary School, in Alamata (Alamata town, Southern Tigray, Tigray). The protestors demanded the schools in the town use Amharic as a language of instruction. Conflicting reports mentioned that protesters argued that schools should remain closed until the conflicts in the Amhara region are resolved. Tigray forces affiliated with TPLF (coded as Tigray Police Force) intervened and killed 2 protestors. 7 - 8 other protestors were injured. Officials from the Tigray regional state claimed that the protesters were armed (uncorroborated). ---- On 6 March 2025, overnight, ENDF soldiers killed 5 civilians (4 Orthodox dogma students and 1 Orthodox dogma teacher in Timuga (Raya Alamata, Southern Tigray, Tigray). The soldiers entered Kidane Mihiret church (Orthodox) and fatally shot the victims, injuring 5 other students. The eyewitness stated that the ENDF received wrong information about the presence of Fano militias in the premises of the church. ---- On 6 March 2025, overnight, ENDF soldiers killed 5 civilians (4 Orthodox dogma students and 1 Orthodox dogma teacher in Timuga (Raya Alamata, Southern Tigray, Tigray). The soldiers entered Kidane Mihiret church (Orthodox) and fatally shot the victims, injuring 5 other students. The eyewitness stated that the ENDF received wrong information about the presence of Fano militias in the premises of the church.</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>2024-05-31 ---- 2024-06-09 ---- 2024-10-01 ---- 2025-03-06 ---- 2025-03-06</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>Southern Tigray</t>
+        </is>
+      </c>
       <c r="BL4" t="n">
         <v>0</v>
       </c>
@@ -1127,7 +1137,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ET0203</t>
+          <t>ET0106</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -1136,58 +1146,58 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ET0206</t>
+          <t>ET0604</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ET0203;ET0206;ET0409;ET0411;ET0412;ET0417;ET1602;ET1603;ET1604;ET1605</t>
+          <t>ET0102;ET0103;ET0106;ET0415;ET0422;ET0604;ET0802</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>76.16051411743817</v>
+        <v>72.70360568058959</v>
       </c>
       <c r="I5" t="n">
-        <v>23.83948588256183</v>
+        <v>26.89260752834676</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.4037867910636499</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>19.73</v>
+        <v>21.08</v>
       </c>
       <c r="M5" t="n">
-        <v>7.62</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="O5" t="n">
-        <v>0.45</v>
+        <v>3.2</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.45</v>
+        <v>0.17</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="V5" t="n">
-        <v>0.45</v>
+        <v>0.34</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
@@ -1237,68 +1247,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ET0206</t>
+          <t>ET0107</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>ET0203</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ET0203;ET0206;ET0409;ET0411;ET0412;ET0417;ET1602;ET1603;ET1604;ET1605</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>100</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>33.94</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.44</v>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
@@ -1326,20 +1298,64 @@
       <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tigray</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>ET01</t>
+        </is>
+      </c>
       <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>Protest with intervention ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>Protesters (Ethiopia) ---- Protesters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>Students (Ethiopia) ---- Muslim Group (Ethiopia); Students (Ethiopia); Women (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Police Forces of Ethiopia (2018-) Tigray State Police</t>
+        </is>
+      </c>
       <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>On 5 April 2024, hundreds of Mekele University main campus students whose graduation was delayed by two years due to the northern Ethiopia conflict staged a protest in Mekele (Mekelle, Mekelle Tigray, Tigray) against the university's decision to postpone their graduation to the next year. Police intervened and dispersed the gathering by firing warning shots and beating students (extent of injuries not reported). An unspecified number of students sustained slight injuries. At least 10 students were arrested. ---- On 21 January 2025, over 10,000 Muslim students, parents and other residents staged a peaceful demonstration at Romanat Square in Mekele (Mekelle Tigray, Tigray), opposing the banning of hijab-wearing female Muslim students from 5 schools in Axum. The 5 schools prevented 159 female Muslim students from classes because of wearing headscarves. The Ethiopian Supreme Council for Islamic Affairs and Tigray Region Supreme Council for Islamic Affairs protested the schools' decision and requested the schools' leadership to stop interfering in religious affairs at various points. The Tigray Region Education Bureau previously wrote a letter instructing the schools to refrain from adding new directives and instructed them to continue teaching with the school regulations that were in action before the ban. Likewise, the court suspended the schools' protocols. According to the protesters, the schools refused to obey the court's order and the education bureau's instruction and continued prohibiting the female students from accessing the schools' compound.</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>2024-04-05 ---- 2025-01-21</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>Mekelle Tigray</t>
+        </is>
+      </c>
       <c r="BL6" t="n">
         <v>0</v>
       </c>
@@ -1347,7 +1363,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ET0409</t>
+          <t>ET0203</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -1356,7 +1372,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ET0417</t>
+          <t>ET0206</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1365,10 +1381,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>87.11060087255598</v>
+        <v>76.16051411743817</v>
       </c>
       <c r="I7" t="n">
-        <v>12.88939912744403</v>
+        <v>23.83948588256183</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1377,28 +1393,28 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>27.23</v>
+        <v>19.73</v>
       </c>
       <c r="M7" t="n">
-        <v>0.17</v>
+        <v>7.62</v>
       </c>
       <c r="N7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5.38</v>
+        <v>0.45</v>
       </c>
       <c r="P7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S7" t="n">
-        <v>0.17</v>
+        <v>0.45</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1407,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
@@ -1457,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ET0411</t>
+          <t>ET0206</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -1466,7 +1482,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ET0412</t>
+          <t>ET0203</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1475,10 +1491,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>92.90612856394127</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>7.093871436058735</v>
+        <v>100</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1487,37 +1503,37 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>16.01</v>
+        <v>33.94</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="N8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.53</v>
+        <v>0.36</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
@@ -1546,60 +1562,20 @@
       <c r="AU8" t="inlineStr"/>
       <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Oromia</t>
-        </is>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>ET04</t>
-        </is>
-      </c>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>Protests</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>Peaceful protest</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>Protesters (Ethiopia)</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
-        </is>
-      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
       <c r="BG8" t="inlineStr"/>
       <c r="BH8" t="inlineStr"/>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>On 22 November 2024, ethnic Oromo students staged a protest at Meda Walabu University in Robe town, Robe (Jimma, Oromia), to demand justice for a young man beheaded by suspected Fano militias in Dera, North Shewa (coded separately). The protesters chanted slogans calling for the government to disarm ethnic Amhara civilians, ensure accountability and protect civilians from violence.</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>Bale</t>
-        </is>
-      </c>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
       <c r="BL8" t="n">
         <v>0</v>
       </c>
@@ -1607,147 +1583,179 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ET0412</t>
+          <t>ET0301</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ET0411</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ET0203;ET0206;ET0409;ET0411;ET0412;ET0417;ET1602;ET1603;ET1604;ET1605</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>66.23873577477266</v>
-      </c>
-      <c r="I9" t="n">
-        <v>33.76126422522734</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>14.83</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="O9" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>January 2025:  An education facility was destroyed by an ENDF drone strike, killing three and wounding three Fano militias based in the school.</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building </t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>Ethiopian National Defense Forces</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Aerial Bomb: Drone</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>Primary School</t>
+        </is>
+      </c>
       <c r="AU9" t="inlineStr"/>
       <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Oromia</t>
+          <t>Amhara</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>ET04</t>
+          <t>ET03</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>Protests</t>
+          <t>Violence against civilians ---- Protests ---- Explosions/Remote violence</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>Peaceful protest</t>
+          <t>Abduction/forced disappearance ---- Excessive force against protesters ---- Air/drone strike</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>Protesters (Ethiopia)</t>
+          <t>Unidentified Armed Group (Ethiopia) ---- Protesters (Ethiopia) ---- Military Forces of Ethiopia (2018-)</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Civilians (Eritrea) ---- Police Forces of Ethiopia (2018-) Amhara State Police ---- Fano Youth Militia</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>Refugees/IDPs (Eritrea)</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>On 22 November 2024, ethnic Oromo students protested at Borena University, Yabelo town, Yabelo (Borena, Oromia). The protesters were joined by Jatani Ali High School students to demand justice for a young man beheaded by suspected Fano militias in Selelkula on 27 August (coded separately). The protesters chanted slogans calling for the government to ensure accountability and condemned its failure to protect civilians.</t>
+          <t>On 4 April 2024, three unknown gunmen (coded as an unidentified armed group) abducted a 12-year-old Eritrean refugee who was returning from school in Dabat town, Dabat (North Gondar, Amhara). The group demanded families a ransom of 800 thousand ETB in exchange for his release. ---- On 19 December 2024, students of Debark University staged a public demonstration on the premises of Debark University in Debark (Debark town, North Gondar, Amhara), protesting the low budget for student meals. The police shot and killed 1 and wounded 2 other students (uncorroborated fatalities). The police also arrested many students and released them on the following day, 20 December 2024. ---- On 9 January 2025, ENDF conducted a drone strike against Fano positions in Cherdikwa Kebele near Debark (Debark town, North Gondar, Amhara), killing 3 and wounding 3 Fano militias. The attack targeted Fano militias based in one unnamed public primary school in the Kebele. According to the Fano representative from the area, the drone strike killed and wounded its members and destroyed the school.</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-04-04 ---- 2024-12-19 ---- 2025-01-09</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>Borena</t>
+          <t>North Gondar</t>
         </is>
       </c>
       <c r="BL9" t="n">
@@ -1757,151 +1765,175 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ET0414</t>
+          <t>ET0302</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ET0414</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ET0414</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>79.73223888020637</v>
-      </c>
-      <c r="I10" t="n">
-        <v>16.85878417029613</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.8663087615858193</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2.542668187911691</v>
-      </c>
-      <c r="L10" t="n">
-        <v>23.14</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>2025-04-02 ---- 2025-03-12 ---- 2024-11-17 ---- 2024-11-17 ---- 2024-11-13 ---- 2024-11-13 ---- 2024-01-24</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">April 2025: An education facility was hit by an Ethiopian National Defense Force (ENDF) drone strike killing 11 people and injuring over 35.  ---- March 2025: A civilian was killed near the entrance of an education facility. ---- As reported November 2024: An educational facility was hit by an ENDF drone strikes. ---- As reported November 2024: An educational facility was hit by an ENDF drone strikes. ---- November 2024: An educational facility was hit by an ENDF drone strike. ---- November 2024: An educational facility was hit by an ENDF drone strike. ---- January 2024: University students and educators prohibited by an unidentified armed group from travelling to a university, following the Ministry of Education's announcement about the resumption of schools due to improved security situations. The group stopped public buses at multiple checkpoints and checked IDs. Some students managed to pass later after being escorted by ENDF soldiers. </t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- On Way To or From School</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>Other ---- No Information ---- Other ---- Other ---- Other ---- Other ---- NSA</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Ethiopian National Defense Forces ---- No Information ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Unidentified Armed Actor</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Aerial Bomb: Drone ---- No Information on the Weapon Used ---- Aerial Bomb: Drone ---- Aerial Bomb: Drone ---- Aerial Bomb: Drone ---- Aerial Bomb: Drone ---- Firearms</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>Primary School ---- Primary School ---- School: No Further Details ---- School: No Further Details ---- Secondary School ---- School: No Further Details ---- Not Applicable</t>
+        </is>
+      </c>
       <c r="AU10" t="inlineStr"/>
       <c r="AV10" t="inlineStr"/>
       <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Oromia</t>
+          <t>Amhara</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>ET04</t>
+          <t>ET03</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>Riots</t>
+          <t>Strategic developments ---- Violence against civilians ---- Strategic developments ---- Battles ---- Battles ---- Explosions/Remote violence</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>Violent demonstration</t>
+          <t>Other ---- Sexual violence ---- Looting/property destruction ---- Armed clash ---- Armed clash ---- Air/drone strike</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>Rioters (Ethiopia)</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>Students (Ethiopia)</t>
-        </is>
-      </c>
+          <t>Fano Youth Militia ---- Military Forces of Ethiopia (2018-) ---- Fano Youth Militia ---- Fano Youth Militia ---- Fano Youth Militia ---- Military Forces of Ethiopia (2018-)</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr"/>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Police Forces of Ethiopia (2018-) Oromia State Police</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr"/>
+          <t>Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Civilians (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>Students (Ethiopia); Teachers (Ethiopia) ---- Students (Ethiopia); Women (Ethiopia) ---- Government of Ethiopia (2018-)</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>On 22 May 2024, elementary school students rioted (means unknown) in Hare Kelo (Gora Dola, Guji, Oromia) opposing sitting for grade 8 regional examination. The rioters claimed that they did not get adequate time to prepare for the examination. The Oromia region police assaulted and arrested 12-13 students who participated in the riot. Extent of injuries unknown/not reported.</t>
+          <t>Other: Around 24 January 2024 (week of), an unnamed armed group (likely Fano militias) stopped public buses at multiple checkpoints in Debre Tabor town (South Gondar, Amhara). The group checked IDs and prohibited university students and teachers from traveling to Mekdela Amba University, following the Ministry of Education's announcement about the resumption of schools due to improved security situations. However, some students who were blocked managed to pass later after being escorted by ENDF soldiers. ---- On 13 July 2024, ENDF soldiers were suspected of raping over 35 secondary school girls (uncorroborated) inside the ENDF military camp in Guna (Guna Begemider, South Gondar, Amhara). The soldiers were escorting the victims who were returning to their home towns in Seden Muja and Semada woredas after taking the national university entrance examination at Debre Tabor University. The perpetrators forced the victims to spend the night with them in the Guna military camp, where they raped the victims. ---- Property destruction: On 26 December 2024, the Amhara region government accused Fano of burning student textbooks with an estimated value of 10 million ETB at Rib in Ebenat Wereda (location coded to the admin center Ibnat, South Gondar, Amhara). The textbooks, owned by the Ebenat Wereda education bureau, were destined for students learning from grades 1 to 12 and were burned by Fano militias as the truck was approaching Ibnat town (14 km away). Fano declined responsibility and stated that its forces had ambushed an ENDF truck that was transporting rations for ENDF soldiers, not textbooks. ---- On 3 March 2025, Fano militias clashed with ENDF in Debre Tabor town (South Gondar, Amhara) and the surrounding areas (coded separately), resulting in an unknown number of fatalities from both sides and the closure of schools and government offices. Fano claimed to have inflicted heavy losses on the ENDF. Fano forces launched the attack from different directions of the town after receiving information that a section of government forces was moving from the town in the direction of Ebnat to attack Fano militias. Unspecified number of fatalities mentioned coded as 10. 10 fatalities split across two locations and coded as 5 for this event. ---- On 3 March 2025, Fano militias clashed with ENDF in unspecified locations around Debre Tabor (South Gondar, Amhara) and in Debre Tabor town (coded separately), resulting in an unknown number of fatalities from both sides and the closure of schools and government offices. Fano claimed to have inflicted heavy losses on ENDF. Fano forces launched the attack from different directions of the town after receiving information that a section of government forces was moving from the town in the direction of Ebnat to attack Fano militias. Unspecified number of fatalities mentioned coded as 10. 10 fatalities split across two locations and coded as 5 for this event. ---- On 2 April 2025, ENDF was accused of conducting a drone strike in Asmera kebele in Iste (location coded to admin center Iste, East Esite, South Gondar), killing 14 civilians (uncorroborated fatalities) and wounding 35 civilians. The drone strike was conducted near Asmera Primary School. Uncorroborated number of fatalities coded as 10.</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-01-24 ---- 2024-07-13 ---- 2024-12-26 ---- 2025-03-03 ---- 2025-03-03 ---- 2025-04-02</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>Guji</t>
+          <t>South Gondar</t>
         </is>
       </c>
       <c r="BL10" t="n">
@@ -1911,147 +1943,176 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ET0415</t>
+          <t>ET0303</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ET0106</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ET0102;ET0103;ET0106;ET0415;ET0422;ET0604;ET0802</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>73.88316240734517</v>
-      </c>
-      <c r="I11" t="n">
-        <v>26.08553403739333</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.03130355526149498</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>24.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>2025-04-25 ---- 2025-04-11 ---- 2025-03-19 ---- 2025-03-19 ---- 2025-03-19 ---- 2025-03-19 ---- 2025-03-12 ---- 2025-03-06 ---- 2025-01-12 ---- 2025-01-12 ---- 2024-11-03 ---- 2024-10-23 ---- 2024-09-01 ---- 2024-09-01</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>25 May 2025: An educator was shot and killed, and another critically injured by ENDF forces. The survivor had their leg amputated. ---- April 2025: Educators were harassed by regime forces, primarily the ENDF, as they patrolled near the facilities housing. ---- March 2025: An education facility where regime troops were stationed was attacked by Fano forces using explosives and heavy rifles. ---- March 2025: An education facility where regime troops were stationed was attacked by Fano forces using explosives and heavy rifles. ---- March 2025: An education facility was occupied by ENDF. ---- March 2025: An education facility was occupied by ENDF. ---- March 2025: An education facility was taken over by the Prosperity Party regime to train junior cadres indefinitely, denying access to other users. ---- March 2025: An educator was wounded by members of the Ethiopian National Defence Forces (ENDF). ---- January 2025: An education facility being used by the Republican Guard was attacked by Fano forces. ---- As reported in January 2025: An education facility was occupied by the Republican Guard. ---- November 2024: A school was looted and destroyed by ENDF soldiers. ---- October 2024: An educational facility was heavily damaged by an ENDF drone, causing educational activities in the area to pause._x000D_
+ ---- September 2024: A secondary school, occupied by ENDF military troops, was ambushed by Fano. ---- As reported in September 2024: A secondary school was occupied by ENDF military troops.</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unspecified Location ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Unspecified Location ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building </t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>Other ---- Other ---- NSA ---- NSA ---- Other ---- Other ---- Political Party ---- Other ---- NSA ---- Other ---- Other ---- Other ---- Multiple ---- Other</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Fano ---- Fano ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Prosperity Party (Ethiopia) ---- Ethiopian National Defense Forces ---- Fano ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces, Fano ---- Ethiopian National Defense Forces</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Firearms ---- Firearms ---- Unspecified Explosive ---- Unspecified Explosive ---- No Information on the Weapon Used ---- No Information on the Weapon Used ---- No Information on the Weapon Used ---- No Information on the Weapon Used ---- Firearms ---- Firearms ---- Firearms ---- Aerial Bomb: Drone ---- Firearms ---- Firearms</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>Not Applicable ---- University ---- Primary School ---- Secondary School ---- Primary School ---- Secondary School ---- University ---- Not Applicable ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- Primary School ---- Secondary School ---- Secondary School</t>
+        </is>
+      </c>
       <c r="AU11" t="inlineStr"/>
       <c r="AV11" t="inlineStr"/>
       <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Oromia</t>
+          <t>Amhara</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>ET04</t>
+          <t>ET03</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>Protests</t>
+          <t>Violence against civilians ---- Battles ---- Explosions/Remote violence</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>Peaceful protest</t>
+          <t>Attack ---- Armed clash ---- Air/drone strike</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>Protesters (Ethiopia)</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+          <t>Military Forces of Ethiopia (2018-) ---- Fano Youth Militia ---- Military Forces of Ethiopia (2018-)</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Civilians (Ethiopia) ---- Military Forces of Ethiopia (2018-)</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>Students (Ethiopia)</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>On 21 November 2024, ethnic Oromo students staged a protest at Bule Hora University, Bule Hora town (West Guji, Oromia), to demand justice for a young man beheaded by suspected Fano militias in Selelkula on 27 August (coded separately). The protesters chanted slogans calling for the government to ensure accountability and protect civilians from violence.</t>
+          <t>On 10 August 2024, suspected ENDF killed 2 students (uncorroborated fatalities) in Mola Giyorgis near Weldiya (Woldiya town, North Wello, Amhara). It is suspected ENDF conducted the killings as retaliation for its soldiers that Fano ambushed at the same place on the same date (coded separately). ---- On 1 September 2024, Fano claimed to have ambushed ENDF military troops stationed in Sirinka secondary school (Habru, North Wello, Amhara). Casualties unknown. ---- Around 23 October 2024 (week of), ENDF carried out a drone strike that struck Keyu Daria Primary School in Raya Kobo Zuria, in Raya Kobo Zuria (location coded to the admin center, Kobo town, Kobo, North Wello, Amhara). The schools were closed. Neither civilians nor Fano militias were around. There were no fatalities. Educational activities in the area have come to a standstill, due to safety concerns from both teachers and parents.</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-08-10 ---- 2024-09-01 ---- 2024-10-23</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>West Guji</t>
+          <t>North Wello</t>
         </is>
       </c>
       <c r="BL11" t="n">
@@ -2061,157 +2122,133 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ET0417</t>
+          <t>ET0304</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ET0412</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ET0203;ET0206;ET0409;ET0411;ET0412;ET0417;ET1602;ET1603;ET1604;ET1605</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>88.79922123147091</v>
-      </c>
-      <c r="I12" t="n">
-        <v>11.20077876852909</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>20.84</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="n">
+        <v>3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>2025-03-16 ---- 2025-03-16 ---- 2024-12-24</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>March 2025: An education facility was used by the Ethiopian National Defence Forces (ENDF) to establish a camp. ---- March 2025: An education facility was used by the Ethiopian National Defence Forces (ENDF) to establish a camp. ---- December 2024: An educational facility was damaged by an ENDF drone strike.</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building  ---- Education Building  ---- Education Building </t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>Other ---- Other ---- Other</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>No Information on the Weapon Used ---- No Information on the Weapon Used ---- Aerial Bomb: Drone</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>Primary School ---- Secondary School ---- School: No Further Details</t>
+        </is>
+      </c>
       <c r="AU12" t="inlineStr"/>
       <c r="AV12" t="inlineStr"/>
       <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Oromia</t>
-        </is>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>ET04</t>
-        </is>
-      </c>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>Violence against civilians</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>Abduction/forced disappearance</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>Police Forces of Ethiopia (2018-) Oromia State Police</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>Kebele Communal Militia (Ethiopia)</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>Civilians (Ethiopia)</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>Students (Ethiopia)</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>Around 11 November 2024 (as reported), Oromia regional state police and Kebele militias stopped around 32 civilians, including 15 students between 11 and 16 ages old, and forcefully abducted them in Shashemene town, Shashamane (West Arsi, Oromia). The government forces took them to a detention center with their school uniforms, stating that they were conscripted into the military.</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>2024-11-11</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>West Arsi</t>
-        </is>
-      </c>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
       <c r="BL12" t="n">
         <v>0</v>
       </c>
@@ -2219,109 +2256,181 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ET0422</t>
+          <t>ET0305</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ET0604</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ET0102;ET0103;ET0106;ET0415;ET0422;ET0604;ET0802</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>59.99360095123959</v>
-      </c>
-      <c r="I13" t="n">
-        <v>36.36756705649405</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.638831992266356</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>13.93</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="n">
+        <v>14</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>61</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>2025-04-24 ---- 2025-04-18 ---- 2025-01-26 ---- 2025-01-12 ---- 2025-01-11 ---- 2024-12-01 ---- 2024-11-24 ---- 2024-11-16 ---- 2024-11-04 ---- 2024-10-31 ---- 2024-10-23 ---- 2024-10-23 ---- 2024-05-12 ---- 2024-05-12 ---- 2024-02-19 ---- 2024-01-12</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>April 2025: Five educators were handcuffed and taken to detention centres during armed clashes between Fano and regime forces. ---- April 2025: An education facility was hit by a drone strike by the ENDF around 6:00 p.m, killing at least 26 people and injuring an unspecified number.  ---- January 2025: An education facility was destroyed by shelling from the ENDF during clashes with the Amhara Fano militia. ---- January 2025: An education facility was hit in an ENDF drone strike causing significant damage. ---- January 2025: An education facility was destroyed by two consecutive ENDF drone strikes. ---- December 2024: An educational facility was hit by an ENDF drone strike, killing two people and injuring another. ---- November 2024: An educational facility was damaged by an ENDF drone strike, killing seven people. ---- As reported November 2024: An educational facility used as a makeshift IDP centre was hit by an ENDF drone strike. ---- November 2024: An educational facility was hit in an ENDF drone strike, killing one person. ---- October 2024: An educational facility was taken over by the ENDF and repurposed as a detention and alleged torture centre. ---- October 2024: An educational facility was damaged by an ENDF drone strike. ---- October 2024: An educational facility was hit by an ENDF airstrike, killing at least 11 people and injuring an unspecified number of others. ---- May 2024: A high school was attacked by Ethiopian government forces. An unspecified number of people were killed and injured. ---- May 2024: A school was hit by an Ethiopian government forces drone strike during a meeting organised by the Parents educators Association (PTA). Four people were killed and five injured. ---- February 2024: around nine ethnic Oromo civilians, including five educators were kidnapped by Fano militias from a public bus. Eight were reportedly shot and killed three days later. ---- January 2024: ENDF drone attack hit near the entrance to a school. The strike was reportedly targeting the alleged presence of Fano militants in a park reportedly utilised by Fano forces for ration and logistics supply.</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unspecified Location ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Private Travel ---- Education Building </t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>No Information ---- Other ---- Other ---- Other ---- Other ---- Other ---- Other ---- Other ---- Other ---- Other ---- Other ---- Other ---- Other ---- Other ---- NSA ---- Other</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>No Information ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Fano ---- Ethiopian National Defense Forces</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Firearms ---- Aerial Bomb: Drone ---- Shelling ---- Aerial Bomb: Drone ---- Aerial Bomb: Drone ---- Aerial Bomb: Drone ---- Aerial Bomb: Drone ---- Aerial Bomb: Drone ---- Aerial Bomb: Drone ---- No Information on the Weapon Used ---- Aerial Bomb: Drone ---- Aerial Bomb: Plane ---- Aerial Bomb: Drone ---- Aerial Bomb: Drone ---- Firearms ---- Aerial Bomb: Drone</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>Not Applicable ---- Primary School ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- Primary School ---- School: No Further Details ---- Primary School ---- Secondary School ---- Primary School ---- Secondary School ---- Secondary School ---- Primary School ---- Not Applicable ---- Secondary School</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>NoInformation ---- Killed, StillInCaptivity</t>
+        </is>
+      </c>
       <c r="AV13" t="inlineStr"/>
       <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="inlineStr"/>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
-      <c r="BA13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Amhara</t>
+        </is>
+      </c>
+      <c r="AY13" t="n">
+        <v>33</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>ET03</t>
+        </is>
+      </c>
       <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>Explosions/Remote violence ---- Violence against civilians ---- Violence against civilians ---- Violence against civilians ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>Air/drone strike ---- Abduction/forced disappearance ---- Attack ---- Abduction/forced disappearance ---- Air/drone strike ---- Air/drone strike ---- Air/drone strike ---- Air/drone strike ---- Air/drone strike ---- Air/drone strike ---- Air/drone strike</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>Military Forces of Ethiopia (2018-) ---- Fano Youth Militia ---- Fano Youth Militia ---- Fano Youth Militia ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-)</t>
+        </is>
+      </c>
       <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
-      <c r="BI13" t="inlineStr"/>
-      <c r="BJ13" t="inlineStr"/>
-      <c r="BK13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Fano Youth Militia ---- Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Fano Youth Militia ---- Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Fano Youth Militia</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>Civilians (Ethiopia); Students (Ethiopia) ---- Oromo Ethnic Group (Ethiopia); Teachers (Ethiopia) ---- Labor Group (Ethiopia); Oromo Ethnic Group (Ethiopia); Teachers (Ethiopia) ---- Teachers (Ethiopia) ---- Farmers (Ethiopia); Teachers (Ethiopia) ---- Civilians (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>On 12 January 2024, ENDF conducted a drone attack in Alem Ketema, Merhabete woreda (North Shewa, Amhara) targeting Karl Recreation Centre, a building used by Fano to store ration and logistics. The attack caused panic among students at the nearby Arbegnoch Comprehensive Secondary School resulting to some students sustaining injuries while trying to escape. 2 Fano were killed and at least 4 civilians were injured by the attack. ---- On 19 February 2024, Fano militias abducted around nine ethnic Oromo civilians, including five teachers and three women domestic workers returning to their families from the Middle East, in Shewa Robit town, Shoa Robit (North Shewa, Amhara). The armed group shot and killed eight of them on 22 February, prompting the SoE command to declare the banning of any movements and closure of the main road between Debre Birhan and Dessie (coded separately). ---- On 22 February 2024, Fano militias shot and killed 8 ethnic Oromo civilians, including five teachers and three women domestic workers returning to their families from the Middle East, in Shewa Robit town, Shoa Robit (North Shewa, Amhara), after kidnapping them from a public bus on 19 February while they were en route to Kemise (coded separately). After the incident, the command post overseeing the state of emergency in the Amhara region has imposed an indefinite ban on all kinds of movement on the main asphalt between Debre Berhan and Dessie cities. ---- On 28 March 2024, over midnight, Fano militias kidnapped the President of Debre Birhan University from his home in Debre Berhan town (North Shewa, Amhara). They held him a hostage for over a month. Motivation unknown/not reported. ---- On 12 May 2024, ENDF carried out a drone attack on Gulo school in Tere kebele (Kewet, North Shewa, Amhara). Conflicting reports stated 2 to 7 civilians were killed, and at least 9 others were injured. Two of the victims (a teacher and a farmer) sustained a serious injury. The victims included people who were attending a parent-teacher meeting in the school and farmers who were in the nearby area. Classrooms and other school properties were also damaged. Fatalities coded as 2, based on EHRC preliminary report. ---- On 23 October 2024, ENDF was accused of conducting a drone strike in Jihur town (Moretna Jiru, North Shewa, Amhara), killing an unspecified number of civilians (uncorroborated). The strike targeted Jihur secondary school and the nearby houses. No further information is available concerning the presence of students or teachers in the school premises at the time of the strike. Unspecified number of fatalities coded as 3. ---- On 23 October 2024, ENDF was accused of conducting a drone strike in Zendogur kebele in Basona Werena wereda (location coded to the nearest admin center Debre Birhan, Debre Berhan town, North Shewa, Amhara). The strike targeted the private house of one Fano leadership member and Zendogur primary school. The strike destroyed the home of the Fano leadership member and partially damaged the school. There were no fatalities. ---- On 4 November 2024, ENDF was accused of conducting a drone strike at a Shola Amba Primary School in Angada Kebele (Angolelana Tera, North Shewa, Amhara), killing 1 civilian (uncorroborated fatality) and many cattle. There were neither students nor teachers on the school premises and the victim was a civilian who was found near the school's compound. ---- On 24 November 2024, ENDF was accused of conducting a drone strike in Kasima Kebele (Basona Worena, North Shewa, Amhara), killing an unspecified number of civilians (uncorroborated fatalities). The strike targeted a primary school located in the Kebele. It is unknown/not reported if the students or teachers were on the school's premises at the time of the strike. Unspecified number of fatalities coded as 3. ---- On 1 December 2024, ENDF conducted a drone strike in Akarmit Kebele (Minjar Shenkora, North Shewa, Amhara), killing an unspecified number of civilians (uncorroborated fatalities). The drone strike targeted Akarmit Primary School. The statement issued by Fano indicated that there were no Fano militia members or any armed persons near the area. It is unknown/not reported whether the students or teachers were among the victims. Unspecified number of fatalities coded as 3. ---- On 6 December 2024, ENDF launched a drone strike targeting Fano militias in Mehal Gob kebele, near Debre Berhan town, Debre Birhan (North Shewa, Amhara). The strike also impacted Bezo school and struck nearby civilian farms. 11 individuals were killed and two others sustained injuries.</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>2024-01-12 ---- 2024-02-19 ---- 2024-02-22 ---- 2024-03-28 ---- 2024-05-12 ---- 2024-10-23 ---- 2024-10-23 ---- 2024-11-04 ---- 2024-11-24 ---- 2024-12-01 ---- 2024-12-06</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>North Shewa</t>
+        </is>
+      </c>
       <c r="BL13" t="n">
         <v>0</v>
       </c>
@@ -2329,109 +2438,181 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ET0604</t>
+          <t>ET0306</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ET0422</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ET0102;ET0103;ET0106;ET0415;ET0422;ET0604;ET0802</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>56.37706578854814</v>
-      </c>
-      <c r="I14" t="n">
-        <v>42.82191582723836</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.8010183842135069</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>38.33</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7.94</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="n">
+        <v>7</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>129</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>2025-04-17 ---- 2025-04-15 ---- 2025-02-04 ---- 2024-12-11 ---- 2024-12-11 ---- 2024-10-22 ---- 2024-10-22</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>April 2025: An education facility was hit by an ENDF drone strike, killing more than 100 people and injuring 24. The local administration stated that they were attacking local Fano militants, not civilians‚Äîdespite the fact that only civilians were killed.  ---- April 2025: An education facility was used as a base by ENDF and its materials were vandalised before they fled.  ---- February 2025: An educational facility was damaged by suspected ENDF soldiers. They broke in and destroyed textbooks and computers.  ---- December 2024: An educational facility was taken over and used by ENDF soldiers. ---- December 2024: An educational facility occupied by ENDF was attacked by Fano fighters. ---- October 2024: An educational facility was hit by an ENDF drone strike. ---- October 2024: An educational facility was hit by an ENDF drone strike, killing two people and injuring at least three others.</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building </t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>Other ---- Other ---- Other ---- Other ---- NSA ---- Other ---- Other</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Fano ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Aerial Bomb: Drone ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Aerial Bomb: Drone ---- Aerial Bomb: Drone</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>Primary School ---- Primary School ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- Secondary School ---- Primary School</t>
+        </is>
+      </c>
       <c r="AU14" t="inlineStr"/>
       <c r="AV14" t="inlineStr"/>
       <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Amhara</t>
+        </is>
+      </c>
+      <c r="AY14" t="n">
+        <v>129</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>ET03</t>
+        </is>
+      </c>
       <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
-      <c r="BI14" t="inlineStr"/>
-      <c r="BJ14" t="inlineStr"/>
-      <c r="BK14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>Battles ---- Violence against civilians ---- Battles ---- Battles ---- Battles ---- Battles ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Strategic developments ---- Battles ---- Strategic developments ---- Battles ---- Explosions/Remote violence</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>Armed clash ---- Attack ---- Armed clash ---- Armed clash ---- Armed clash ---- Armed clash ---- Air/drone strike ---- Air/drone strike ---- Other ---- Armed clash ---- Looting/property destruction ---- Armed clash ---- Air/drone strike</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>Military Forces of Ethiopia (2018-) ---- Fano Youth Militia ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Fano Youth Militia ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-)</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>Police Forces of Ethiopia (2018-) Amhara Regional Riot Police</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Fano Youth Militia ---- Civilians (Ethiopia) ---- Fano Youth Militia ---- Fano Youth Militia ---- Fano Youth Militia ---- Fano Youth Militia ---- Civilians (Ethiopia) ---- Fano Youth Militia ---- Civilians (Ethiopia) ---- Fano Youth Militia ---- Civilians (Ethiopia) ---- Fano Youth Militia ---- Civilians (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>Teachers (Ethiopia) ---- Civilians (Ethiopia); Farmers (Ethiopia) ---- Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>On 18 August 2024, ENDF supported by Amhara Riot Police exchanged gunfire with Fano in the areas around the Prison administration and Teachers' college in Debre Markos (Debre Markos town, East Gojam, Amhara). Casualties unknown. ---- On 18 September 2024, Fano members killed 2 Irob Gebeya General Secondary School teachers in Rebu Gebeya in Senan Woreda (East Gojam, Amhara). The perpetrators accused the victims of taking the initiative to register students for the 2017 Ethiopian academic year and participating in the organization of the school year's commencement plan. The Foreign Relations and Diaspora Division head of Gojam Fano denied targeting teachers based on their profession alone, but indicated that it would continue taking measures against individuals collaborating with the enemy forces. ---- Around 27 September 2024 (as reported), ENDF clashed with Fano militia in Gindewoin (Goncha Siso Enebse, East Gojam, Amhara), and Bichena, Shebel Bernta and Mertule Mariam (coded separately). Fano militia attempted to disrupt school openings and the delivery of other public services. Casualties unknown. ENDF arrested 67 individuals after accusing them of providing logistics for Fano. 40 Fano militants surrendered to ENDF. 101 Kalashnikov guns, 73 Pistols, 10 outdated guns, 4 grenade bombs, 188 Kalashnikov cases, 20 Mechetes, 16 waist armaments, and 3667 explosives were seized. ---- Around 27 September 2024 (as reported), ENDF clashed with Fano militia in Bichena (Bechena town, East Gojam, Amhara), and Shebel Bernta, Mertule Mariam, and Gindewoin (coded separately). Fano militia attempted to disrupt school openings and the delivery of other public services. Casualties unknown. ENDF arrested 67 individuals after accusing them of providing logistics for Fano. 40 Fano militants surrendered to ENDF. 101 Kalashnikov guns, 73 Pistols, 10 outdated guns, 4 grenade bombs, 188 Kalashnikov cases, 20 Mechetes, 16 waist armaments, and 3667 explosives were seized. ---- Around 27 September 2024 (as reported), ENDF clashed with Fano militia in Shebel Bernta woreda (location coded to the admin center of the woreda, Yeidwuha, East Gojam, Amhara), and Bichena, Mertule Mariam and Gindewoin (coded separately). Fano militia attempted to disrupt school openings and the delivery of other public services. Casualties unknown. ENDF arrested 67 individuals after accusing them of providing logistics for Fano. 40 Fano militants surrendered to ENDF. 101 Kalashnikov guns, 73 Pistols, 10 outdated guns, 4 grenade bombs, 188 Kalashnikov cases, 20 Mechetes, 16 waist armaments, and 3667 explosives were seized. ---- Around 27 September 2024 (as reported), ENDF clashed with Fano militia in Mertule Mariam (Enebse Sarmder Woreda, East Gojam, Amhara), and Shebel Bernta, Bichena, and Gindewoin (coded separately). Fano militia attempted to disrupt school openings and the delivery of other public services. Casualties unknown. ENDF arrested 67 individuals after accusing them of providing logistics for Fano. 40 Fano militants surrendered to ENDF. 101 Kalashnikov guns, 73 Pistols, 10 outdated guns, 4 grenade bombs, 188 Kalashnikov cases, 20 Mechetes, 16 waist armaments, and 3667 explosives were seized. ---- On 15 October 2024, ENDF was accused of conducting a drone strike at Asteriyo school in Motta (Hulet Ej Enese, East Gojam, Amhara), killing at least 5 civilians. There is no further information available. ---- On 22 October 2024, ENDF was accused of conducting a drone strike in Felege Birhan (Enarj Enawga, East Gojam, Amhara), killing 1 Fano militia and 13 farmers (uncorroborated fatalities), damaging two farmers' houses and parts of Niwaye- Mariam primary school. The drone strike likely targeted Fano soldiers who were present in or near the Niwaye-Mariam primary school. Uncorroborated fatalities coded as 10. ---- Non-violent activity: On 23 October 2024, Fano militias blocked the main road in Amanuel town, Michakel (East Gojam, Amhara), and forced over 300 Injibara University students, mostly ethnic Oromo students, to return to Debre Markos. Debremarkos University administration offered shelter and told them to stay and wait for the command post to escort them back to Injibara University. ---- Around 2 February 2025 (as reported), ENDF claimed to have clashed with a Fano militia based in Aba Girar school in Yegosa Giorgis Kebele (Enarj Enawga, East Gojam, Amhara). ENDF further claimed to have killed 26 militants, and captured 2 others (uncorroborated fatalities coded as 10). 4 Bren guns, 2 automatic guns, 7 outdated guns, 4 communication radios, 230 DShK bullets, 300 Bren bullets, 66 Kalashnikov bullets and 1 military eyeglass were seized. ---- Property destruction: On 4 February 2025, suspected ENDF soldiers damaged textbooks and computers stored in a public school (Kork number 2 school) in Kork Kebele of Baso Liben wereda (Baso Liben, East Gojam, Amhara). According to the school's guard, the perpetrators entered offices by breaking doors. ---- On 13 March 2025, ENDF clashed with Fano militias in Darji, Enebse Sarmder (Goncha Siso Enebse,East Gojam, Amhara), and Tanta (coded separately). The clashes began when the ENDF attempted to reclaim institutions held by Fano militants, including a school in Derji kebele, which led to further exchanges of gunfire. This confrontation resulted in an unknown number of casualties among civilians. An unspecified number of fatalities coded as 3. 3 fatalities split and shared across the two locations (coded separately) and coded as 2 for this event. ---- On 17 April 2025, the ENDF conducted a drone strike in Gedeb town (Enarj Enawga, East Gojam, Amhara), killing over 100 civilians. According to Gojam Amhara Fano's representative, the drone strike was the government's response to stop the Fano movement in the locality, as Fano recently started to operate in the area. The eyewitness testimonies indicated that the drone strike targeted civilians who were volunteering to construct a fence for Gedeb Primary School. According to the head of the Enarj Enawga Wereda administration, the drone strike targeted the Fano militia, not civilians. Further, an ENDF commander from the area indicated that the attack targeted Fano militias gathered in the area to welcome Fano leaders in Gojam.</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>2024-08-18 ---- 2024-09-18 ---- 2024-09-27 ---- 2024-09-27 ---- 2024-09-27 ---- 2024-09-27 ---- 2024-10-15 ---- 2024-10-22 ---- 2024-10-23 ---- 2025-02-02 ---- 2025-02-04 ---- 2025-03-13 ---- 2025-04-17</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>East Gojam</t>
+        </is>
+      </c>
       <c r="BL14" t="n">
         <v>0</v>
       </c>
@@ -2439,109 +2620,186 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ET0802</t>
+          <t>ET0307</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ET0106</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ET0102;ET0103;ET0106;ET0415;ET0422;ET0604;ET0802</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>96.88832831100149</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.932561032380277</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.1791106566182307</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>16.63</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="inlineStr"/>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AU15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="n">
+        <v>16</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>83</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>2025-03-25 ---- 2025-03-19 ---- 2025-02-20 ---- 2025-02-19 ---- 2025-02-19 ---- 2025-02-19 ---- 2025-02-19 ---- 2025-02-12 ---- 2025-02-06 ---- 2025-01-12 ---- 2024-12-22 ---- 2024-11-29 ---- 2024-11-09 ---- 2024-11-08 ---- 2024-11-05 ---- 2024-10-08 ---- 2024-08-16 ---- 2024-08-16 ---- 2024-06-16 ---- 2024-04-04</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">March 2025: An educational facility was partially destroyed when suspected ENDF soldiers shelled Fano positions with cannon fire. ---- March 2025: An education facility where regime troops were stationed was attacked by Fano forces. ---- February 2025:An education facility occupied by the ENDF was attacked by the engineer brigade of the Fano militia. Eventually the ENDF brought reinforcements from elsewhere and the Fano fighters withdrew their attack. ---- February 2025: An education facility was taken over by the ENDF and turned into their military camp following fighting with Fano fighters. ---- February 2025: 12 educators were abducted by Fano militias, in an attempt to prevent schools opening. The victims were released after an ransom of unknown amount was paid. ---- February 2025: 11 educators were abducted by Fano militias, in an attempt to prevent schools opening. The victims were released after an ransom of unknown amount was paid. ---- February 2025: Two educators were abducted by Fano militias, in an attempt to prevent schools opening. ---- February 2025: 13 educators were abducted from an educational facility by Fano militia and taken to the desert. The facility reopened after the government assured protection for the educators. ---- February 2025: An education facility was hit by a drone strike from the ENDF. ---- January 2025: An education facility was damaged by an ENDF drone strike. ---- December 2024: An educational facility was taken over and used by Fano fighters. ---- November 2024: Educators and students injured by an explosion by ENDF soldiers at an educational facility. ---- November 2024: An educational facility was hit by an ENDF drone strike, killing around 11 people and injuring four others. ---- November 2024: An educational facility was hit in an ENDF drone strike, killing nine people. ---- November 2024: An educational facility was hit by an ENDF drone attack. 13 children were killed. ---- October 2024: An educational facility was hit by an ENDF airstrike, killing an unspecified number of people. ---- As reported in August 2024: Fano Forces stationed in an elementary school were attacked by the ENDF. ---- As reported in August 2024: An elementary school was occupied by Fano forces. ---- June 2024: An unspecified number of educators were killed during clashes between Fano and ENDF forces.  ---- April 2024: 25 students were injured in an explosion at a prep school carried out by a student who was part of an armed group._x000D_
+</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Unspecified Location ---- Unspecified Location ---- Unspecified Location ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Unspecified Location ---- Education Building </t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>Other ---- NSA ---- NSA ---- Other ---- NSA ---- NSA ---- NSA ---- NSA ---- Other ---- Other ---- NSA ---- Other ---- Other ---- Other ---- Other ---- Other ---- Other ---- NSA ---- Multiple ---- NSA</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>Ethiopian National Defense Forces ---- Fano ---- Fano ---- Ethiopian National Defense Forces ---- Fano ---- Fano ---- Fano ---- Fano ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Fano ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Fano ---- Ethiopian National Defense Forces, Fano ---- Unidentified Armed Actor</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>Shelling ---- No Information on the Weapon Used ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Aerial Bomb: Plane ---- Aerial Bomb: Drone ---- Firearms ---- Unspecified Explosive ---- Aerial Bomb: Drone ---- Aerial Bomb: Drone ---- Aerial Bomb: Drone ---- Aerial Bomb: Plane ---- Firearms ---- No Information on the Weapon Used ---- Firearms ---- Unspecified Explosive</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>Secondary School ---- School: No Further Details ---- Secondary School ---- Secondary School ---- Not Applicable ---- Not Applicable ---- Not Applicable ---- Primary School ---- Primary School ---- School: No Further Details ---- Primary School ---- Primary School ---- Primary School ---- School: No Further Details ---- Primary School ---- Primary School ---- Primary School ---- Primary School ---- Not Applicable ---- Primary School</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>Freed ---- Freed ---- NoInformation ---- NoInformation</t>
+        </is>
+      </c>
       <c r="AV15" t="inlineStr"/>
       <c r="AW15" t="inlineStr"/>
-      <c r="AX15" t="inlineStr"/>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Amhara</t>
+        </is>
+      </c>
+      <c r="AY15" t="n">
+        <v>128</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>30</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>ET03</t>
+        </is>
+      </c>
       <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
-      <c r="BI15" t="inlineStr"/>
-      <c r="BJ15" t="inlineStr"/>
-      <c r="BK15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>Explosions/Remote violence ---- Violence against civilians ---- Violence against civilians ---- Violence against civilians ---- Battles ---- Explosions/Remote violence ---- Violence against civilians ---- Battles ---- Strategic developments ---- Violence against civilians ---- Strategic developments ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Violence against civilians ---- Explosions/Remote violence ---- Battles ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Strategic developments ---- Battles ---- Explosions/Remote violence ---- Violence against civilians ---- Battles ---- Violence against civilians ---- Violence against civilians ---- Violence against civilians ---- Violence against civilians ---- Battles ---- Explosions/Remote violence ---- Explosions/Remote violence</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>Grenade ---- Abduction/forced disappearance ---- Attack ---- Attack ---- Armed clash ---- Grenade ---- Attack ---- Armed clash ---- Change to group/activity ---- Attack ---- Arrests ---- Grenade ---- Air/drone strike ---- Abduction/forced disappearance ---- Air/drone strike ---- Armed clash ---- Air/drone strike ---- Air/drone strike ---- Other ---- Government regains territory ---- Air/drone strike ---- Abduction/forced disappearance ---- Armed clash ---- Abduction/forced disappearance ---- Abduction/forced disappearance ---- Abduction/forced disappearance ---- Abduction/forced disappearance ---- Armed clash ---- Shelling/artillery/missile attack ---- Grenade</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>Fano Youth Militia ---- Fano Youth Militia ---- Military Forces of Ethiopia (2018-) ---- Fano Youth Militia ---- Fano Youth Militia ---- Fano Youth Militia ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Fano Youth Militia ---- Military Forces of Ethiopia (2018-) ---- Fano Youth Militia ---- Military Forces of Ethiopia (2018-) ---- Fano Youth Militia ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Fano Youth Militia ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Fano Youth Militia ---- Military Forces of Ethiopia (2018-) ---- Fano Youth Militia ---- Fano Youth Militia ---- Fano Youth Militia ---- Fano Youth Militia ---- Fano Youth Militia ---- Military Forces of Ethiopia (2018-) ---- Fano Youth Militia</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>Police Forces of Ethiopia (2018-) Amhara State Police</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Military Forces of Ethiopia (2018-) ---- Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Fano Youth Militia ---- Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Fano Youth Militia ---- Military Forces of Ethiopia (2018-) ---- Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Fano Youth Militia ---- Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Fano Youth Militia ---- Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Military Forces of Ethiopia (2018-) ---- Fano Youth Militia ---- Military Forces of Ethiopia (2018-)</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>Students (Ethiopia) ---- Government of Ethiopia (2018-); Teachers (Ethiopia) ---- Farmers (Ethiopia); Orthodox Christian Group (Ethiopia); Students (Ethiopia) ---- Labor Group (Ethiopia); Teachers (Ethiopia) ---- Students (Ethiopia) ---- Labor Group (Ethiopia); Teachers (Ethiopia) ---- Students (Ethiopia) ---- Labor Group (Ethiopia); NaMA: National Movement of Amhara; PP: Prosperity Party; Teachers (Ethiopia) ---- Protestant Christian Group (Ethiopia) ---- Government of Ethiopia (2018-) ---- Civilians (Ethiopia) ---- Kebele Communal Militia (Ethiopia); Police Forces of Ethiopia (2018-) Amhara State Police ---- Students (Ethiopia); Health Workers (Ethiopia); Farmers (Ethiopia); Christian Group (Ethiopia) ---- Farmers (Ethiopia) ---- Teachers (Ethiopia) ---- Teachers (Ethiopia); Women (Ethiopia) ---- Teachers (Ethiopia) ---- Teachers (Ethiopia) ---- Teachers (Ethiopia) ---- Civilians (Ethiopia) ---- Aid Workers (Ethiopia); Judges (Ethiopia); Police Forces of Ethiopia (2018-) Federal Police</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>On 6 February 2024, gunmen (likely Fano, mentioned as rebels and due to the location of the event) entered Bahir Dar University Tibebe Ghion Medical Campus and started firing bullets near a student's dormitory in Bahir Dar (Bahir Dar town, West Gojam, Amhara). The perpetrators exploded a hand bomb near the student cafeteria simultaneously with the firing. There were no civilian targets, but the perpetrators hit the female students' dormitory (blocks 1 and 3) multiple times with stray bullets. The perpetrators gathered students and instructed them to leave the campus. There were no fatalities. ---- On 11 February 2024, Fano militias kidnapped an unspecified number of teachers, school directors, and Woreda Education Department supervisors in an unspecified location (coded to admin center, Liben) in Semen Achefer woreda (West Gojam, Amhara), when they were returning to Liben town from campaigning for students to get back-to-schools. The armed group released the hostages two days later after warning them not to further engage in promoting the Prosperity Party's agenda. ---- On 28 February 2024, ENDF soldiers summarily executed 11 civilians (10 students and 1 farmer) who were attending their Kine (poetry) education at Ethiopian Orthodox Church South Gojam Diocese St. Gabriel church in Birakat (Debub Mecha, West Gojam, Amhara). The perpetrators accused the victims of hosting Fanos in the church compound and of sympathizing with Fano. Some sources placed the number of fatalities at 33. ---- Around 12 March 2024 (as reported), suspected Fano militia killed at least 8 civilians (fatalities uncorroborated), including 2 local administrators, a teacher, a hotel worker, a hotel owner, and 2 children, in Mer Awi (Merawi Town, West Gojam, Amhara), after clashing with ENDF (coded separately). ---- On 14 March 2024, Fano and ENDF clashed in Tis Abay (Bahirdar Zuria, West Gojam, Amhara). Fano targeted the ENDF faction stationed in the compound of Tis Abay school and Mebrat Hail. Fano claimed to have killed many ENDF soldiers and indicated that one of its members was killed in the clash, and four other members sustained injuries. An unspecified number of fatalities coded as 4 (1 Fano member and 3 for an unspecified number of ENDF soldiers killed by Fano). ---- On 4 April 2024, Fano threw a hand bomb on Damot Preparatory School in Finote Selam (Finote Selam town, West Gojam, Amhara), injuring at least 24 people. Other reports mentioned that up to 31 students were injured. The bomb was thrown by a student who allegedly received instruction from and was coordinated by Fano. There were no fatalities. ---- On 16 June 2024, ENDF attacked civilians near the Goha Hotel, Dembecha neighborhood, in Jiga town (Jabi Tehnan, Western Gojam, Amhara). Conflicting reports mentioned fatalities ranging from 13 - 20 civilians, and 2 others were injured. The killing happened following a clash between Fano and ENDF forces (coded separately). Teachers and bankers were among the victims. ---- Around 16 August 2024 (as reported), ENDF claimed to have carried out military operations against Fano stationed at Yizora Elementary School in Yizora kebele (Yilmana Densa Woreda, West Gojam, Amhara). ENDF further claimed that 69 militants were killed and more than 50 others were injured (uncorroborated fatalities coded as 10). 16 Kalashnikovs, 2 SKS guns, 3 outdated guns, 1 mortar carrier, 1 FSR truck, 2 Sino trucks, several bullets and other armament were seized. ENDF patrolled areas in Debre May, Densa Bata, Mestayat, Rob Gebeya, Tsion, and Chinkulit before launching this attack (coded separately). ---- Movement of forces: Around 16 August 2024 (as reported), ENDF patrolled areas in Debre May, Densa Bata, Mestayat, Rob Gebeya, Tsion and Chinkulit Kebeles (locations coded to the zonal Admin center, Bahir Dar, Bahir Dar town, West Gojam, Amhara), before attacking Fano Forces stationed in Yizora Elementary School (coded separately). ---- On 18 August 2024, suspected ENDF soldiers killed 22 civilians (uncorroborated fatalities) in Bahir Dar (Bahir Dar town, West Gojam, Amhara). The perpetrators conducted the attack as a retaliation for Fano's operation in the Bahir Dar town and surrounding towns (coded separately). Among the victims, 5 were university students. Uncorroborated fatalities coded as 10. ---- Around 2 October 2024 (week of), the ENDF and Amhara state police arrested over 100 individuals in various major towns of the Amhara region (location coded to the regional admin center Bahir Dar, Bahir Dar town, West Gojam, Amhara). The arrested include university teachers, civil servants, business owners, opposition political party members, and other segments of society. A House of Peoples Representative member who joined the house representing the National Movement of Amhara (NaMA) and another Amhara Region State Council member who joined the council representing the Prosperity Party were among the victims. The mass arrest started on 28 September 2024 and continued over the week. The government of the Amhara region and ENDF indicated that they have jointly started a law enforcement operation across the region and will continue taking measures against individuals who provide information and logistics support for rebels. The arrests were made without a court order and, in some cases, during night raids. ---- On 4 October 2024, an unidentified armed group (likely Fano due to their involvement in similar activities) set off grenades in multiple neighborhoods of Bahir Dar town, Bahir Dar (West Gojam, Amhara). One of the attacks targeted the Adventist school in the city. The Human Rights Commission urged everyone to avoid targeting civilians and civilian institutions and to refrain from disrupting the residents' daily activities. Casualties unknown. ---- On 8 October 2024, ENDF was accused of conducting a drone strike in Kolela kebele in North Mecha wereda (location coded to admin center Mer Awi, Merawi town, West Gojam, Amhara). The drone strike targeted one unnamed school located in the kebele. There were no fatalities. ---- On 9 October 2024, Fano abducted at least 80 civilians in Feres Bet (Dega Damot, West Gojam, Amhara), after accusing them of being information sources for government forces. The armed group also burned down and destroyed 3 houses including a residential house of the Woreda Administrator. The perpetrators killed 38 of them near Michael school in Feres Bet on 6 December 2024 (coded separately), after receiving a ransom ranging from 100,000 to 1 million ETB from the victims' families. Some victims were civil servants who were serving in various public offices in different capacities before the perpetrators abducted them. ---- On 15 October 2024, ENDF conducted a drone strike near Dega Damot Woreda police station in Feres Bet town (Dega Damot, West Gojam, Amhara), likely targeting Fano militants who were keeping kidnapped civilians at the police station. The strike partly damaged the Commercial Bank of Ethiopia's branch building, hit a nearby residential house, and killed 1 child. The militants relocated the detainees to Gomata school following the attack by ENDF. ---- On 19 October 2024, Fano claimed to have clashed with enemy forces (likely the ENDF, Amhara State Police, and Kebele militia due to the area of the clash and context) in Kunzila (Semen Achefer, West Gojam, Amhara). The Fano entered the town and started the clash as the government security forces met with teachers, persuading them to begin teaching. Casualties are unknown. ---- On 5 November 2024, ENDF carried out three rounds of drone attacks targeting a marketplace, an elementary school and a health center in Zihibist (Arge) town (Debub Achefer, West Gojam, Amhara). At least 43 people were killed, and 21 others were injured. Students, nurses, farmers and churchgoers were among the victims. Residents claimed that there were no clashes in the area during the attack and the city remained under government control. ---- On 8 November 2024, ENDF was accused of conducting a drone strike against Birr Adma school in Gebeze Mariam (Quarit, West Gojam, Amhara), killing 9 civilians (uncorroborated fatalities). ---- Other: On 5 December 2024, Fano militants relocated 37 kidnapped civilians from Gomata school to Michael school in Feres Bet town (Dega Damot, West Gojam, Amhara), following a clash with ENDF on 4 December 2024 (coded separately). 6 of the detainees were released on the same day. 31 individuals were killed on 6 December 2024 (coded separately). ---- On 6 December 2024, ENDF clashed with Fano militia and recaptured Feres Bet town (Dega Damot, West Gojam, Amhara). Casualties unknown. Fano militia killed 31 individuals it kidnapped and kept at Michael school, after losing control of the town to ENDF (coded separately). ---- On 24 December 2024, ENDF was accused of conducting a drone strike in Shurba Bifeta (Sekela, West Gojam, Amhara), killing 7 farmers (uncorroborated fatalities). The drone targeted and destroyed Shurba Primary School, and the victims were local residents who were working on their farm near the school. There were no students in the premises of the school. ---- Around 2 January 2025 (as reported), Fano militants abducted 14 teachers from Meshenti Secondary School (Bahirdar Zuria, West Gojam, Amhara), as an objection to school opening in the area. ENDF intervened and rescued the teachers from the militants after an armed clash (coded separately). ---- Around 2 January 2025 (as reported), ENDF clashed with Fano militia at an unspecified location in Bahirdar Zuria Woreda (location coded to Meshenti, Bahir Dar Zuria, West Gojam, Amhara), after the militants abducted 14 teachers. The teacher who were abducted by the militants to prevent school from opening were all rescued by the ENDF. Casualties unknown. ---- On 12 February 2025, Fano militia abducted 13 teachers (5 male and 8 female) from Kore Elementary School in Kore Tenkere Kebele (Gonje Kolela, North Gojam, Amhara) and took them to Tegoda desert. Fano militias were preventing school openings in the region, frequently abducted teachers who did not comply with their order and demanded up to 50,000 Ethiopian Birr payment to release them. The school was opened after the government gave assurance to provide protection to teachers. Fano released all of the victims on 20 February 2024. ---- Around 19 February 2025 (as reported), Fano abducted 12 teachers in Mer Awi (Merawi town, West Gojam, Amhara). Fano militias were preventing school openings in the region and frequently abducted teachers who did not comply with their order. The perpetrators released the victims after receiving ransom (the ransom amount is unknown/not reported). ---- On 19 February 2025, Fano abducted 2 teachers at an unspecified place in Gonje Wereda (location coded to the admin center Gonje Kolela, West Gojam, Amhara). Fano militias were preventing school openings in the region by frequently abducting teachers who did not comply with their order to not open schools. Further information not available. ---- Around 19 February 2025 (as reported), Fano abducted 11 teachers at an unspecified place in Gonje Wereda (location coded to the admin center Gonje Kolela, West Gojam, Amhara). Fano militias were preventing school openings in the region by frequently abducting teachers who did not comply with their order. The perpetrators released the victims after receiving ransom (the ransom amount is unknown/not reported). ---- On 20 March 2025, Fano clashed with ENDF in Mer Awi (Merawi town, West Gojam, Amhara), killing and wounding many government soldiers (uncorroborated fatalities). Further, Fano executed 9 civilians, including four teachers and a former mayor of Merawi, after entering the town. One of the teachers was killed while entering the school gate to begin lessons. The other teachers and the former mayor were taken from their homes and killed. A community-based health insurance coordinator was also abducted by the armed forces. The spokesperson of Amhara Fano in Gojam contends that the victims were not civilians, but 'enemy collaborators'. The clash was the continuation of a joint operation dubbed 'Unity Operation' launched around the same day by Amhara Fano in Gondar, Amhara Fano in Shewa, Amhara Fano in Gojjam, and Bete Amhara or Amhara Fano in Wello. The ENDF accused Brigadier General Migbe Haile of masterminding the operation. The Tigray Bureau of Peace and Security denied the accusation as 'mere allegations and defamation.' ---- On 25 March 2025, suspected ENDF soldiers shelled (with cannon) Fano positions in Aklay, Debre Weyifat, and Kenchel Kebeles near Adet (Adete town, West Gojam, Amhara), wounding 2 civilians (a mother and child), and partially destroying St. Gabriel secondary school. There were no fatalities. ---- On 8 April 2025, suspected Fano militia threw four hand bombs in Bahir Dar (Bahir Dar town, West Gojam, Amhara). The bomb attacks were conducted at four different places within Bahir Dar town, targeting the ENDF vehicle transporting soldiers, the federal police office, a vehicle transporting Amhara state supreme court officials, and a UNICEF vehicle. The first two bomb attacks killed many ENDF soldiers and federal police members (uncorroborated fatalities). The third attack that targeted the Amhara state Supreme Court vehicle wounded the court officials. The fourth bomb targeted the UN vehicle that was parked near the UNICEF office. The federal government communication minister accused the Fano militia of conducting the attack on the UNICEF vehicle and abducting the staff to prevent the school from reopening in the region. Fano confirmed the first three bomb attacks, but declined the accusation concerning the fourth attack and accused the ENDF of throwing a hand bomb at the UN vehicle to accuse Fano of terrorism charges. Unspecified number of fatalities coded as 3.</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>2024-02-06 ---- 2024-02-11 ---- 2024-02-28 ---- 2024-03-12 ---- 2024-03-14 ---- 2024-04-04 ---- 2024-06-16 ---- 2024-08-16 ---- 2024-08-16 ---- 2024-08-18 ---- 2024-10-02 ---- 2024-10-04 ---- 2024-10-08 ---- 2024-10-09 ---- 2024-10-15 ---- 2024-10-19 ---- 2024-11-05 ---- 2024-11-08 ---- 2024-12-05 ---- 2024-12-06 ---- 2024-12-24 ---- 2025-01-02 ---- 2025-01-02 ---- 2025-02-12 ---- 2025-02-19 ---- 2025-02-19 ---- 2025-02-19 ---- 2025-03-20 ---- 2025-03-25 ---- 2025-04-08</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>West Gojam</t>
+        </is>
+      </c>
       <c r="BL15" t="n">
         <v>0</v>
       </c>
@@ -2549,109 +2807,179 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ET1601</t>
+          <t>ET0309</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ET1601</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ET1601</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>91.74523834390045</v>
-      </c>
-      <c r="I16" t="n">
-        <v>8.254761656099554</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr"/>
-      <c r="AQ16" t="inlineStr"/>
-      <c r="AR16" t="inlineStr"/>
-      <c r="AS16" t="inlineStr"/>
-      <c r="AT16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="n">
+        <v>8</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>2025-05-20 ---- 2025-05-20 ---- 2025-05-07 ---- 2025-05-07 ---- 2024-12-13 ---- 2024-12-13 ---- 2024-12-09 ---- 2024-12-09 ---- 2024-11-19 ---- 2024-09-25</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">May 2025: An education facility was taken over by the ENDF. ---- May 2025: An education facility was attacked by Fano fighters targeting the ENDF inside the facility. ---- May 2025: An education facility was struck by Fano forces after it had been encamped by the ENDF. ---- As reported May 2025: An education facility was encamped by the ENDF. ---- December 2024: Teachers were forcibly gathered for a meeting with ENDF soldiers. ---- December 2024: During a meeting between teachers and the ENDF, FANO militia started firing nearby. Some of the ENDF soldiers were injured. ---- December 2024: An educational facility used by unidentified perpetrators to detain ENDF soldiers was hit by an ENDF drone strike. _x000D_
+ ---- December 2024: An educational facility was taken over and used by suspected Fano fighters to detain ENDF soldiers. ---- November 2024: An educational facility was set on fire by the ENDF. ---- September 2024: A primary school was hit by Ethiopian National Defense Force (ENDF) air strike._x000D_
+</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Unspecified Location ---- Unspecified Location ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building </t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Other ---- NSA ---- NSA ---- Other ---- Other ---- NSA ---- Other ---- NSA ---- Other ---- Other</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>Ethiopian National Defense Forces ---- Fano ---- Fano ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Fano ---- Ethiopian National Defense Forces ---- Fano ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>Firearms ---- Firearms ---- Unspecified Explosive ---- Firearms ---- Firearms ---- Firearms ---- Aerial Bomb: Drone ---- Firearms ---- Arson ---- Aerial Bomb: Plane</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>Secondary School ---- Secondary School ---- Secondary School ---- Secondary School ---- Not Applicable ---- Not Applicable ---- Primary School ---- Primary School ---- Primary School ---- Primary School</t>
+        </is>
+      </c>
       <c r="AU16" t="inlineStr"/>
       <c r="AV16" t="inlineStr"/>
       <c r="AW16" t="inlineStr"/>
-      <c r="AX16" t="inlineStr"/>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr"/>
-      <c r="BA16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Amhara</t>
+        </is>
+      </c>
+      <c r="AY16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>ET03</t>
+        </is>
+      </c>
       <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Strategic developments ---- Battles</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>Air/drone strike ---- Air/drone strike ---- Air/drone strike ---- Other ---- Armed clash</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Fano Youth Militia</t>
+        </is>
+      </c>
       <c r="BF16" t="inlineStr"/>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
-      <c r="BI16" t="inlineStr"/>
-      <c r="BJ16" t="inlineStr"/>
-      <c r="BK16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Civilians (Ethiopia) ---- Fano Youth Militia ---- Fano Youth Militia ---- Military Forces of Ethiopia (2018-)</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>Orthodox Christian Group (Ethiopia); Students (Ethiopia) ---- Civilians (Ethiopia) ---- Kebele Communal Militia (Ethiopia); Police Forces of Ethiopia (2018-) Amhara Regional Riot Police</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>On 25 September 2024, the ENDF was accused of conducting a drone strike at Dimama (Fagta Lakoma, Awi, Amhara). The strike was conducted near Dimama Primary School . Casualties unknown. ---- On 17 October 2024, ENDF conducted a drone strike in Afesa Kebele of Dangila wereda (Awi, Amhara), killing at least 10 civilians and many cattle. Many of the victims were religious students (Abinet school students) studying Orthodox Church theology. ---- On 9 December 2024, the Ethiopian Airforce launched drone strikes targeting the Gojam Fano positions in Fagta Lakoma primary school/Fogota (Awi, Amhara). 14 people including 12 ENDF soldiers who were captured in a clash the day before (coded separately) and two women who were serving meals for these captured soldiers were killed and 11 others (including 9 captured ENDF soldiers) were injured by the strike. ---- Other: Around 14 February 2025 (as reported), ENDF seized 51 Computer CPUs, 41 Desktop computers, 1 copy machine, 1 solar machine, 44 plastic chairs, 21 plastic tables, 177 metal sheets, 12 wraps of wire, 2 metals and various speakers and music player devices looted and stored by Fano militia in Abadra Elementary school (Abadra Agaga, Dangila, Awi, Amhara). The equipment were looted from various government and private institutions and stored in the school. ---- On 20 May 2025, Fano claimed to have clashed with ENDF, Amhara regional riot police, and Kebele militia in Tilili (Guagusa Shikudad, Awi, Amhara), killing at least 10 government security forces (uncorroborated fatalities). The clash started when the Fano militia ambushed a school that the government security forces were using as a temporary camp. The clash continued on 21 May 2025 (coded separately).</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>2024-09-25 ---- 2024-10-17 ---- 2024-12-09 ---- 2025-02-14 ---- 2025-05-20</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>Awi</t>
+        </is>
+      </c>
       <c r="BL16" t="n">
         <v>0</v>
       </c>
@@ -2659,109 +2987,177 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ET1602</t>
+          <t>ET0311</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ET1604</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ET0203;ET0206;ET0409;ET0411;ET0412;ET0417;ET1602;ET1603;ET1604;ET1605</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>98.60079548273832</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.399204517261678</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>17.44</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr"/>
-      <c r="AT17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="n">
+        <v>6</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>67</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>2025-05-02 ---- 2025-03-21 ---- 2025-03-21 ---- 2025-02-17 ---- 2024-11-30 ---- 2024-11-07 ---- 2024-09-26 ---- 2024-09-17</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>May 2025: 67 students were forcibly conscripted by the ENDF. ---- March 2025: An education facility where regime troops had established a fortified military position was attacked by Fano forces. ---- March 2025: An education facility was occupied by regime troops who established a fortified military position. ---- February 2025: An education facility was hit by a drone attack from the ENDF. An unspecified number of people were killed. ---- November 2024: Intense fighting between Fano militia and ENDF erupted at an education facility.  ---- November 2024: An educational facility was hit in an ENDF drone strike, killing 37 people and injuring 17 others. ---- September 2024: Six persons were killed and four others injured after the high school after a drone attack carried out by the ENDF. The school was also damaged. ---- September 2024: An unspecified number of students were killed and injured during fighting between Fano fighters and regime forces in a school.</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building </t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>Other ---- NSA ---- Other ---- Other ---- Multiple ---- Other ---- Other ---- Multiple</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>Ethiopian National Defense Forces ---- Fano ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces, Fano ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces ---- Ethiopian National Defense Forces, Fano</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>Firearms ---- No Information on the Weapon Used ---- No Information on the Weapon Used ---- Aerial Bomb: Drone ---- Firearms, Mortar ---- Aerial Bomb: Drone ---- Aerial Bomb: Drone ---- Firearms</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>Secondary School ---- University ---- University ---- Primary School ---- Secondary School ---- School: No Further Details ---- Secondary School ---- School: No Further Details</t>
+        </is>
+      </c>
       <c r="AU17" t="inlineStr"/>
       <c r="AV17" t="inlineStr"/>
       <c r="AW17" t="inlineStr"/>
-      <c r="AX17" t="inlineStr"/>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr"/>
-      <c r="BA17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Amhara</t>
+        </is>
+      </c>
+      <c r="AY17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>ET03</t>
+        </is>
+      </c>
       <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Violence against civilians ---- Battles ---- Strategic developments</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>Attack ---- Attack ---- Armed clash ---- Arrests</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>Kebele Communal Militia (Ethiopia) ---- Unidentified Armed Group (Ethiopia) ---- Military Forces of Ethiopia (2018-) ---- Government of Ethiopia (2018-)</t>
+        </is>
+      </c>
       <c r="BF17" t="inlineStr"/>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
-      <c r="BI17" t="inlineStr"/>
-      <c r="BJ17" t="inlineStr"/>
-      <c r="BK17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Fano Youth Militia ---- Fano Youth Militia</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>Students (Ethiopia) ---- Orthodox Christian Group (Ethiopia); Teachers (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>On 8 July 2024, suspected government security forces (likely Kebele communal militia) shot and killed 2 students (uncorroborated fatalities) near Amba Giorgis (Wegera, Central Gondar, Amhara). 5 other students were wounded due to the attack. The students were traveling to Amba Giorgis town for a national examination. ---- On 17 September 2024, the Central Gondar Diocese of Ethiopian Orthodox Tewahdo church accused an armed actor (coded as an unidentified armed group) of entering Mekane Hiywot Bezawit church (orthodox) and killing 1 church servant (minister and teacher) in Gonder (Gonder town, Central Gondar, Amhara). Another church servant was wounded. ---- Around 6 March 2025 (as reported), ENDF claimed to have clashed with Fano militia at an unspecified location in East Belesa Woreda (location coded to the admin center, Gohala, Central Gondar, Amhara). ENDF accused the militants of carrying out attacks on educational and agricultural institutions in the area. According to the ENDF, an unspecified number of militants were killed (fatalities uncorroborated). Unspecified number of fatalities coded as 3. ENDF also claimed to have seized 3 RF vehicles, an ambulance, a motorbike, a printer machine, a photocopy machine, and teff. ---- Around 24 April 2025 (as reported), the Gonder town administration peace and security office (coded as the government of Ethiopia) arrested 3 Fano members who were attempting to commit 'terrorism crimes' and disturb public peace in Gonder (Gonder town, Central Gondar, Amhara). The Fano members were arrested together with an unspecified number of explosive devices as they were attempting to explode schools, market areas, and other public spaces. The statement from the Gonder town administration peace and security office indicated that the arrested Fano members had previously bombed the police office and Kebele administration office with explosive devices (coded separately) and were attempting to conduct the same crime.</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>2024-07-08 ---- 2024-09-17 ---- 2025-03-06 ---- 2025-04-24</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>Central Gondar</t>
+        </is>
+      </c>
       <c r="BL17" t="n">
         <v>0</v>
       </c>
@@ -2769,68 +3165,30 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ET1603</t>
+          <t>ET0312</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ET0203</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ET0203;ET0206;ET0409;ET0411;ET0412;ET0417;ET1602;ET1603;ET1604;ET1605</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>98.56841068818423</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.431589311815775</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
@@ -2858,20 +3216,64 @@
       <c r="AU18" t="inlineStr"/>
       <c r="AV18" t="inlineStr"/>
       <c r="AW18" t="inlineStr"/>
-      <c r="AX18" t="inlineStr"/>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr"/>
-      <c r="BA18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Amhara</t>
+        </is>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>ET03</t>
+        </is>
+      </c>
       <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>Abduction/forced disappearance</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>Qemant Ethnic Militia (Ethiopia)</t>
+        </is>
+      </c>
       <c r="BF18" t="inlineStr"/>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
-      <c r="BI18" t="inlineStr"/>
-      <c r="BJ18" t="inlineStr"/>
-      <c r="BK18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Civilians (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>Teachers (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>On 2 May 2025, the Qemant Ethnic Militia abducted 15 civilians in Kumer (Metema, West Gondar, Amhara). The victims were traveling from Aykel to Negade Behar in a public bus. Some victims were teachers teaching at Negade Behar secondary and primary schools.</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>West Gondar</t>
+        </is>
+      </c>
       <c r="BL18" t="n">
         <v>0</v>
       </c>
@@ -2879,109 +3281,177 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ET1604</t>
+          <t>ET0401</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ET1602</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ET0203;ET0206;ET0409;ET0411;ET0412;ET0417;ET1602;ET1603;ET1604;ET1605</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>96.36249574924338</v>
-      </c>
-      <c r="I19" t="n">
-        <v>3.637504250756623</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>17.05</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="inlineStr"/>
-      <c r="AQ19" t="inlineStr"/>
-      <c r="AR19" t="inlineStr"/>
-      <c r="AS19" t="inlineStr"/>
-      <c r="AT19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">August 2024: A educator was shot and killed and two other people injured by suspected OLF-OLA who accused them of hiding ENDF soldiers. </t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>Unspecified Location</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>Oromo Liberation Army</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Firearms</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="AU19" t="inlineStr"/>
       <c r="AV19" t="inlineStr"/>
       <c r="AW19" t="inlineStr"/>
-      <c r="AX19" t="inlineStr"/>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr"/>
-      <c r="BA19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="AY19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>ET04</t>
+        </is>
+      </c>
       <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Violence against civilians ---- Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>Attack ---- Attack ---- Attack</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- OLF-OLA: Oromo Liberation Army-Oromo Liberation Front</t>
+        </is>
+      </c>
       <c r="BF19" t="inlineStr"/>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
-      <c r="BI19" t="inlineStr"/>
-      <c r="BJ19" t="inlineStr"/>
-      <c r="BK19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Civilians (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>Teachers (Ethiopia) ---- Prisoners (Ethiopia); Students (Ethiopia) ---- Teachers (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>On 10 April 2024, suspected government forces (coded as ENDF) shot and killed a teacher of Chisa Boru High School in Yubdo, Yubdo woreda (West Wellega, Oromia). The motive is unknown/not reported. ---- Around 15 May 2024 (as reported), ENDF arrested and killed a student at an unspecified location in Gudetu Kondole Woreda (location coded to the admin center of the Woreda, Kondala, West Wellega, Oromia). Motivation unknown. ---- On 19 August 2024, suspected OLF-OLA fighters shot and killed 1 teacher (uncorroborated fatality) and wounded 2 others in Sombo Sadan Gitan kebele, Leta Sibu woreda (West Wellega, Oromia), after accusing them of hiding ENDF soldiers.</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>2024-04-10 ---- 2024-05-15 ---- 2024-08-19</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>West Wellega</t>
+        </is>
+      </c>
       <c r="BL19" t="n">
         <v>0</v>
       </c>
@@ -2989,110 +3459,5362 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ET1605</t>
+          <t>ET0402</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ET1602</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ET0203;ET0206;ET0409;ET0411;ET0412;ET0417;ET1602;ET1603;ET1604;ET1605</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>94.10772236368</v>
-      </c>
-      <c r="I20" t="n">
-        <v>5.89227763632001</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>19.51</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="inlineStr"/>
-      <c r="AR20" t="inlineStr"/>
-      <c r="AS20" t="inlineStr"/>
-      <c r="AT20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>2024-06-06 ---- 2024-02-13</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>June 2024: A educator, a civil servant and a motorbike driver were killed by Fano militia while travelling on a motorbike.  ---- February 2024: A educator was shot and wounded when suspected Oromia regional security forces opened fire on a bus transporting university students and educators while they were travelling to an educational tour. The bus was accused of not stopping at the checkpoint.</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>Private Travel ---- Other</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>NSA ---- NSA</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>Fano ---- Oromo Liberation Army</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>Firearms ---- Firearms</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>Not Applicable ---- Not Applicable</t>
+        </is>
+      </c>
       <c r="AU20" t="inlineStr"/>
       <c r="AV20" t="inlineStr"/>
       <c r="AW20" t="inlineStr"/>
-      <c r="AX20" t="inlineStr"/>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr"/>
-      <c r="BA20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="AY20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>ET04</t>
+        </is>
+      </c>
       <c r="BB20" t="inlineStr"/>
-      <c r="BC20" t="inlineStr"/>
-      <c r="BD20" t="inlineStr"/>
-      <c r="BE20" t="inlineStr"/>
-      <c r="BF20" t="inlineStr"/>
-      <c r="BG20" t="inlineStr"/>
-      <c r="BH20" t="inlineStr"/>
-      <c r="BI20" t="inlineStr"/>
-      <c r="BJ20" t="inlineStr"/>
-      <c r="BK20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Violence against civilians ---- Violence against civilians ---- Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>Attack ---- Attack ---- Attack ---- Peaceful protest ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>Police Forces of Ethiopia (2018-) Oromia State Police ---- OLF-OLA: Oromo Liberation Army-Oromo Liberation Front ---- Fano Youth Militia ---- Protesters (Ethiopia) ---- Protesters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>Oromo Ethnic Group (Ethiopia); Students (Ethiopia) ---- Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- Civilians (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>Students (Ethiopia); Teachers (Ethiopia) ---- Teachers (Ethiopia) ---- Teachers (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>On 13 February 2024, security forces (coded as Oromia regional state police) opened fire on a bus transporting 36 students and six teachers of Nekemte University at a checkpoint in Gute town, Wayu Tuka (East Wellega, Oromia) while they were traveling to Adama for an educational tour. One teacher was shot, wounded, and taken to Nekemt Hospital. The bus was accused of not stopping at the checkpoint. There were no fatalities. ---- Around 15 May 2024 (month of), OLF-OLA killed 2 civilians at unspecified locations in Kiremu Woreda (locations coded to the admin center of the woreda, Kiremu, East Wellega, Oromia). The victims were a teacher and a local Aba Geda (traditional leader). Motivation unknown. ---- On 6 June 2024, Fano militia killed 3 civilians in Chefe Gudina Kebele in Kiremu Woreda (East Wellega, Oromia). Motivation unknown. The victims were a teacher, a civil servant and a motorbike driver. They were riding on a motorbike. ---- On 21 November 2024, ethnic Oromo students staged a protest at Wellega University, Nekemte town, Nekemt (East Wellega, Oromia), to demand justice for a young man beheaded by suspected Fano militias in Selelkula on 27 August (coded separately). The protesters chanted slogans calling for the government to ensure accountability and protect civilians from violence. ---- On 22 November 2024, ethnic Oromo students at Sire high school protested in Sire town, SIbu Sire (East Wellega, Oromia), to demand justice for a young man beheaded by suspected Fano militias in Dera, North Shewa (coded separately). The protesters chanted slogans calling for the government to ensure accountability and condemned its failure to protect civilians.</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>2024-02-13 ---- 2024-05-15 ---- 2024-06-06 ---- 2024-11-21 ---- 2024-11-22</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>East Wellega</t>
+        </is>
+      </c>
       <c r="BL20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ET0403</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>ET04</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>Protesters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>On 21 November 2024, ethnic Oromo students staged a protest at Metu University, Metu town (Ilu Aba Bora, Oromia), to demand justice for a young man beheaded by suspected Fano militias in Selelkula on 27 August (coded separately). The protesters chanted slogans calling for the government to ensure accountability and protect civilians from violence.</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>Ilu Aba Bora</t>
+        </is>
+      </c>
+      <c r="BL21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ET0404</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>ET04</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>Protesters (Ethiopia) ---- Protesters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>Oromo Ethnic Group (Ethiopia); Students (Ethiopia) ---- Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>On 21 November 2024, ethnic Oromo students staged a protest at Jimma University, Jimma town, Jima (Jimma, Oromia), to demand justice for a young man beheaded by suspected Fano militias in Selelkula on 27 August (coded separately). The protesters chanted slogans calling for the government to ensure accountability and protect civilians from violence. The police forces blocked the gates to prevent the protesters from leaving their campus (no interaction with protesters was reported). ---- On 22 November 2024, ethnic Oromo students staged a protest at Jimma University's Agaro campus in Agaro town (Jimma, Oromia) to demand justice for a young man beheaded by suspected Fano militias in Selelkula on 27 August (coded separately). The protesters chanted slogans calling for the government to ensure accountability and protect civilians from violence.</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>2024-11-21 ---- 2024-11-22</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>Jimma</t>
+        </is>
+      </c>
+      <c r="BL22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ET0405</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>ET04</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>Battles ---- Explosions/Remote violence ---- Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>Armed clash ---- Shelling/artillery/missile attack ---- Protest with intervention ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Protesters (Ethiopia) ---- Protesters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>Oromo Ethnic Group (Ethiopia); Students (Ethiopia) ---- Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>OLF-OLA: Oromo Liberation Army-Oromo Liberation Front ---- Civilians (Ethiopia) ---- Police Forces of Ethiopia (2018-) Oromia State Police</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>Teachers (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>On 20 May 2024, ENDF clashed with OLF-OLA in Leweso kebele Ginde Beret woreda (West Shewa, Oromia), resulting in civilian homes being destroyed and several residents being displaced. The government forces fired artilleries into the villages and aerial strikes hit and partially damaged a primary school. Casualties unknown. ---- Around 29 May 2024 (week of), artilleries fired by suspected ENDF soldiers hit a school in Koricha Cobi kebele (location coded to Chobi) in Cobi woreda (West Shewa, Oromia), resulting in four teachers being injured. No further information is available. ---- On 21 November 2024, ethnic Oromo students staged a protest at Ambo University, Ambo town (West Shewa, Oromia), to demand justice for a young man beheaded by suspected Fano militias in Selelkula on 27 August (coded separately). The protesters chanted slogans calling for the government to ensure accountability and protect civilians from violence. The police forces blocked the gates to prevent the protesters from leaving their campus, some students were reportedly injured by security forces that dispersed the protest. Extent of injuries unknown/not reported. ---- On 22 November 2024, ethnic Oromo students protested in Ginchi, Dendi (West Shewa, Oromia), to demand justice for a young man beheaded by suspected Fano militias in Selelkula on 27 August (coded separately). The protesters chanted slogans calling for the government to ensure accountability, disarm ethnic Amhara militias, and condemned its failure to protect Oromo civilians.</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>2024-05-20 ---- 2024-05-29 ---- 2024-11-21 ---- 2024-11-22</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>West Shewa</t>
+        </is>
+      </c>
+      <c r="BL23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ET0406</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="AY24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>ET04</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Violence against civilians ---- Battles ---- Violence against civilians ---- Battles ---- Violence against civilians ---- Protests ---- Battles ---- Battles</t>
+        </is>
+      </c>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>Attack ---- Attack ---- Armed clash ---- Attack ---- Armed clash ---- Attack ---- Peaceful protest ---- Armed clash ---- Armed clash</t>
+        </is>
+      </c>
+      <c r="BE24" t="inlineStr">
+        <is>
+          <t>Fano Youth Militia ---- OLF-OLA: Oromo Liberation Army-Oromo Liberation Front ---- Military Forces of Ethiopia (2018-) ---- OLF-OLA: Oromo Liberation Army-Oromo Liberation Front ---- Military Forces of Ethiopia (2018-) ---- OLF-OLA: Oromo Liberation Army-Oromo Liberation Front ---- Protesters (Ethiopia) ---- OLF-OLA: Oromo Liberation Army-Oromo Liberation Front ---- OLF-OLA: Oromo Liberation Army-Oromo Liberation Front</t>
+        </is>
+      </c>
+      <c r="BF24" t="inlineStr">
+        <is>
+          <t>Kebele Communal Militia (Ethiopia); Police Forces of Ethiopia (2018-) Oromia State Police ---- Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG24" t="inlineStr">
+        <is>
+          <t>Civilians (Ethiopia) ---- Civilians (Ethiopia) ---- OLF-OLA: Oromo Liberation Army-Oromo Liberation Front ---- Civilians (Ethiopia) ---- Fano Youth Militia ---- Civilians (Ethiopia) ---- Police Forces of Ethiopia (2018-) Oromia State Police ---- Military Forces of Ethiopia (2018-)</t>
+        </is>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>Teachers (Ethiopia) ---- Students (Ethiopia) ---- Students (Ethiopia) ---- Kebele Communal Militia (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>On 27 January 2024, Fano shot and injured two individuals in an unspecified location (coded to Kurkura) in Gerar Jarso woreda (North Shewa, Oromia). The militias had entered several villages, causing insecurity and forcing teachers from 19 primary schools to flee to neighboring towns. The motive behind the attack is unknown. There were no fatalities. ---- On 2 March 2024, OLF-OLA intercepted a public bus traveling from Selelkula to Salayish, killed one civilian (a teacher), and abducted other passengers at an unspecified place between the two locations (location coded to Selelkula, Dera, North Shewa, Oromia). Further information is not available. ---- On 2 July 2024, ENDF supported by Oromia state police and Kebele militia clashed with OLF-OLA at an unspecified location around Gebre Guracha (Kuyu, North Shewa, Oromia) in an attempt to rescue more than 100 university students who were abducted by the militants (coded separately). Casualties unknown. ---- On 2 July 2024, OLF-OLA kidnapped at least 100 university students who were returning home from Debark and Bahir Dar Universities at an unspecified location near Gebre Guracha (Kuyu Woreda, North Shewa, Oromia). The students were traveling on three buses when they were stopped by the abductors, who then proceeded to beat them with sticks and forced them out of the buses. The militants demanded 700,000 Ethiopian Birr ransom for each student. At least 6 students escaped after they were kidnapped. Security forces arrived and clashed with the militants to rescue the students (coded separately). The militants released some of the students on 4 July 2024. ---- On 31 July 2024, federal government forces (likely ENDF due to their deployment in the area) clashed with Fano militias in Mekefta Meneyu kebele, Dera woreda (North Shewa, Oromia). Around 400 grade 12 students who had taken their high school leaving exam at Fiche, Salale University were stranded and forced to stay due to fighting and security concerns. Casualties unknown. ---- On 10 September 2024, OLF-OLA beat and killed 3 students in Were Gebro kebele, Dera (North Shewa, Oromia), and their bodies were later found on the outskirts of Were Gebro. The armed group accused the three individuals of having links with government forces. ---- On 21 November 2024, ethnic Oromo students staged a protest at Salale University, Fiche town, Fiche (North Shewa, Oromia), to demand justice for a young man beheaded by suspected Fano militias in Selelkula on 27 August (coded separately). The protesters chanted slogans calling for the government to ensure accountability and protect civilians from violence. ---- On 19 February 2025, OLF-OLA clashed with government security forces (likely Oromia state police and Kebele militia from the location and context as the security forces were escorting wereda level government leaders) at Silimi in Adisge Kebele (Gerar Jarso, North Shewa, Oromia), killing two individuals (the head of Gerar Jarso Health Office and the head of Gerar Jarso Wereda Prosperity party). The head of the woreda's Prosperity Party also ran into a rocky cliff and was severely injured while trying to escape from the shooting. He was admitted to Fiche Hospital and died on 2025-02-20 while receiving treatment. The victims were returning from a visit to a local public school. ---- On 3 July 2025, OLF-OLA ambushed ENDF convoys who were escorting students returning from their national exams at Selale University at an unspecified place (location coded to admin center, Degem Hambiso) in Degem (North Shewa, Oromia), killing at least 7 ENDF soldiers. No further information is available.</t>
+        </is>
+      </c>
+      <c r="BJ24" t="inlineStr">
+        <is>
+          <t>2024-01-27 ---- 2024-03-02 ---- 2024-07-02 ---- 2024-07-02 ---- 2024-07-31 ---- 2024-09-10 ---- 2024-11-21 ---- 2025-02-19 ---- 2025-07-03</t>
+        </is>
+      </c>
+      <c r="BK24" t="inlineStr">
+        <is>
+          <t>North Shewa</t>
+        </is>
+      </c>
+      <c r="BL24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ET0407</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="n">
+        <v>2</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>2025-03-16 ---- 2025-03-16</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>March 2025: An education facility where regime troops were stationed was attacked by Fano forces. ---- March 2025: An education facility was occupied by ENDF troops who set up a logistics and command centre.</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building  ---- Education Building </t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>NSA ---- Other</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>Fano ---- Ethiopian National Defense Forces</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>No Information on the Weapon Used ---- No Information on the Weapon Used</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>School: No Further Details ---- School: No Further Details</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>ET04</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>Battles ---- Battles ---- Protests</t>
+        </is>
+      </c>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>Armed clash ---- Armed clash ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE25" t="inlineStr">
+        <is>
+          <t>Military Forces of Ethiopia (2018-) ---- Military Forces of Ethiopia (2018-) ---- Protesters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF25" t="inlineStr">
+        <is>
+          <t>Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>OLF-OLA: Oromo Liberation Army-Oromo Liberation Front ---- OLF-OLA: Oromo Liberation Army-Oromo Liberation Front</t>
+        </is>
+      </c>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>On 15 April 2024, government security forces (likely ENDF due to their involvement in security operations in the area) clashed with OLF-OLA for two days (15 and 16 April 2024) on the main road from Kera school to Batu town police station in Batu (Ziway) town (Adama Tulu Jido Kombolcha, East Shewa, Oromia). Casualties unknown. Movement of people and transportation services were disrupted due to the clashes. ---- On 16 April 2024, and for a second day, government security forces (likely ENDF due to their involvement in security operation in the area) clashed with OLF-OLA on the main road from Batu police station to Kera school in Batu (Ziway) town (Adama Tulu Jido Kombolcha, East Shewa, Oromia). Casualties unknown. Movement of people and transportation services were disrupted due to the clashes. ---- On 22 November 2024, ethnic Oromo students staged a protest at Adama Science and Technology University, Adama town (East Shewa, Oromia), to demand justice for a young man beheaded by suspected Fano militias in Selelkula on 27 August (coded separately). The protesters chanted slogans calling for the government to ensure, peace, and accountability, and protect Oromia civilians from violence.</t>
+        </is>
+      </c>
+      <c r="BJ25" t="inlineStr">
+        <is>
+          <t>2024-04-15 ---- 2024-04-16 ---- 2024-11-22</t>
+        </is>
+      </c>
+      <c r="BK25" t="inlineStr">
+        <is>
+          <t>East Shewa</t>
+        </is>
+      </c>
+      <c r="BL25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ET0408</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>ET04</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE26" t="inlineStr">
+        <is>
+          <t>Protesters (Ethiopia) ---- Protesters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF26" t="inlineStr">
+        <is>
+          <t>Students (Ethiopia) ---- Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>On 26 March 2024, Arsi University Dinsho campus students staged a public demonstration in Asela (Asela town, Arsi, Oromia), opposing the killings of Wello Oromos in the Oromo special zone of the Amhara region (coded separately). ---- On 21 November 2024, ethnic Oromo students staged a protest at Arsi University, Asela town, Asela (Arsi, Oromia), to demand justice for a young man beheaded by suspected Fano militias in Selelkula on 27 August (coded separately). The protesters chanted slogans calling for the government to ensure accountability and protect civilians from violence.</t>
+        </is>
+      </c>
+      <c r="BJ26" t="inlineStr">
+        <is>
+          <t>2024-03-26 ---- 2024-11-21</t>
+        </is>
+      </c>
+      <c r="BK26" t="inlineStr">
+        <is>
+          <t>Arsi</t>
+        </is>
+      </c>
+      <c r="BL26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ET0409</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ET0417</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ET0203;ET0206;ET0409;ET0411;ET0412;ET0417;ET1602;ET1603;ET1604;ET1605</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>87.11060087255598</v>
+      </c>
+      <c r="I27" t="n">
+        <v>12.88939912744403</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>27.23</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O27" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr"/>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
+      <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="inlineStr"/>
+      <c r="BJ27" t="inlineStr"/>
+      <c r="BK27" t="inlineStr"/>
+      <c r="BL27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ET0410</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>ET04</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>Strategic developments ---- Protests</t>
+        </is>
+      </c>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>Arrests ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE28" t="inlineStr">
+        <is>
+          <t>Police Forces of Ethiopia (2018-) Oromia State Police ---- Protesters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF28" t="inlineStr">
+        <is>
+          <t>Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG28" t="inlineStr">
+        <is>
+          <t>Civilians (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>Oromo Ethnic Group (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>On 21 June 2024, Oromia regional police arrested around 80 Wakefana religious followers (an indigenous religion of ethnic Oromos) including 25 religious teachers and leaders in Babile (East Hararge, Oromia), after raiding their venue where they were holding their mid-year religious assembly. Local officials accused the detained people of convening a meeting without permission. Followers of the Waqeffanna religion have long complained about difficulties in acquiring land for worship and burial grounds throughout Oromia. 2 people who went to enquire about the arrest were also detained. ---- On 21 November 2024, ethnic Oromo students staged a protest at Haramaya University, Haro Maya (East Hararge, Oromia), to demand justice for a young man beheaded by suspected Fano militias in Selelkula on 27 August (coded separately). The protesters chanted slogans calling for the government to ensure accountability and protect civilians from violence.</t>
+        </is>
+      </c>
+      <c r="BJ28" t="inlineStr">
+        <is>
+          <t>2024-06-21 ---- 2024-11-21</t>
+        </is>
+      </c>
+      <c r="BK28" t="inlineStr">
+        <is>
+          <t>East Hararge</t>
+        </is>
+      </c>
+      <c r="BL28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ET0411</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ET0412</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ET0203;ET0206;ET0409;ET0411;ET0412;ET0417;ET1602;ET1603;ET1604;ET1605</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>92.90612856394127</v>
+      </c>
+      <c r="I29" t="n">
+        <v>7.093871436058735</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>ET04</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE29" t="inlineStr">
+        <is>
+          <t>Protesters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF29" t="inlineStr">
+        <is>
+          <t>Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG29" t="inlineStr"/>
+      <c r="BH29" t="inlineStr"/>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>On 22 November 2024, ethnic Oromo students staged a protest at Meda Walabu University in Robe town, Robe (Jimma, Oromia), to demand justice for a young man beheaded by suspected Fano militias in Dera, North Shewa (coded separately). The protesters chanted slogans calling for the government to disarm ethnic Amhara civilians, ensure accountability and protect civilians from violence.</t>
+        </is>
+      </c>
+      <c r="BJ29" t="inlineStr">
+        <is>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="BK29" t="inlineStr">
+        <is>
+          <t>Bale</t>
+        </is>
+      </c>
+      <c r="BL29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ET0412</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ET0411</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ET0203;ET0206;ET0409;ET0411;ET0412;ET0417;ET1602;ET1603;ET1604;ET1605</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>66.23873577477266</v>
+      </c>
+      <c r="I30" t="n">
+        <v>33.76126422522734</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O30" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>ET04</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE30" t="inlineStr">
+        <is>
+          <t>Protesters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF30" t="inlineStr">
+        <is>
+          <t>Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG30" t="inlineStr"/>
+      <c r="BH30" t="inlineStr"/>
+      <c r="BI30" t="inlineStr">
+        <is>
+          <t>On 22 November 2024, ethnic Oromo students protested at Borena University, Yabelo town, Yabelo (Borena, Oromia). The protesters were joined by Jatani Ali High School students to demand justice for a young man beheaded by suspected Fano militias in Selelkula on 27 August (coded separately). The protesters chanted slogans calling for the government to ensure accountability and condemned its failure to protect civilians.</t>
+        </is>
+      </c>
+      <c r="BJ30" t="inlineStr">
+        <is>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="BK30" t="inlineStr">
+        <is>
+          <t>Borena</t>
+        </is>
+      </c>
+      <c r="BL30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ET0413</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="AY31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>ET04</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>Protests ---- Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Attack</t>
+        </is>
+      </c>
+      <c r="BE31" t="inlineStr">
+        <is>
+          <t>Protesters (Ethiopia) ---- Kebele Communal Militia (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF31" t="inlineStr">
+        <is>
+          <t>Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG31" t="inlineStr">
+        <is>
+          <t>Civilians (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BH31" t="inlineStr"/>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>On 22 November 2024, ethnic Oromo students staged a protest at Ambo University's Waliso campus, Woliso town (South West Shewa, Oromia), to demand justice for a young man beheaded by suspected Fano militias in Selelkula on 27 August (coded separately). The protesters chanted slogans calling for the government to ensure, peace, and accountability and protect civilians in the region. ---- On 26 July 2025, Kebele militias shot and killed 2 youths and injured another one in Teji town, Ilu Woreda (South West Shewa, Oromia), after being accused of planning to organize protests in several towns across South West Shewa, including Woliso town, over territorial disputes in Oromia and neighboring regions. The militiamen had previously warned them to change their hairstyles. Local sources confirm that the two victims were Grade 11 students, while the injured one is a student from Asosa University who had come home for the summer break.</t>
+        </is>
+      </c>
+      <c r="BJ31" t="inlineStr">
+        <is>
+          <t>2024-11-22 ---- 2025-07-26</t>
+        </is>
+      </c>
+      <c r="BK31" t="inlineStr">
+        <is>
+          <t>South West Shewa</t>
+        </is>
+      </c>
+      <c r="BL31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ET0414</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ET0414</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ET0414</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>79.73223888020637</v>
+      </c>
+      <c r="I32" t="n">
+        <v>16.85878417029613</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.8663087615858193</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.542668187911691</v>
+      </c>
+      <c r="L32" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>ET04</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr"/>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>Riots</t>
+        </is>
+      </c>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>Violent demonstration</t>
+        </is>
+      </c>
+      <c r="BE32" t="inlineStr">
+        <is>
+          <t>Rioters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF32" t="inlineStr">
+        <is>
+          <t>Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG32" t="inlineStr">
+        <is>
+          <t>Police Forces of Ethiopia (2018-) Oromia State Police</t>
+        </is>
+      </c>
+      <c r="BH32" t="inlineStr"/>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>On 22 May 2024, elementary school students rioted (means unknown) in Hare Kelo (Gora Dola, Guji, Oromia) opposing sitting for grade 8 regional examination. The rioters claimed that they did not get adequate time to prepare for the examination. The Oromia region police assaulted and arrested 12-13 students who participated in the riot. Extent of injuries unknown/not reported.</t>
+        </is>
+      </c>
+      <c r="BJ32" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="BK32" t="inlineStr">
+        <is>
+          <t>Guji</t>
+        </is>
+      </c>
+      <c r="BL32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ET0415</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ET0106</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ET0102;ET0103;ET0106;ET0415;ET0422;ET0604;ET0802</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>73.88316240734517</v>
+      </c>
+      <c r="I33" t="n">
+        <v>26.08553403739333</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.03130355526149498</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>ET04</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr"/>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE33" t="inlineStr">
+        <is>
+          <t>Protesters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF33" t="inlineStr">
+        <is>
+          <t>Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG33" t="inlineStr"/>
+      <c r="BH33" t="inlineStr"/>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>On 21 November 2024, ethnic Oromo students staged a protest at Bule Hora University, Bule Hora town (West Guji, Oromia), to demand justice for a young man beheaded by suspected Fano militias in Selelkula on 27 August (coded separately). The protesters chanted slogans calling for the government to ensure accountability and protect civilians from violence.</t>
+        </is>
+      </c>
+      <c r="BJ33" t="inlineStr">
+        <is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="BK33" t="inlineStr">
+        <is>
+          <t>West Guji</t>
+        </is>
+      </c>
+      <c r="BL33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ET0416</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>ET04</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr"/>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE34" t="inlineStr">
+        <is>
+          <t>Protesters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF34" t="inlineStr">
+        <is>
+          <t>Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="inlineStr"/>
+      <c r="BI34" t="inlineStr">
+        <is>
+          <t>On 22 November 2024, ethnic Oromo students at Weyesa Secondary School protested in Bedele town, Bedele (Buno Bedele, Oromia), to demand justice for a young man beheaded by suspected Fano militias in Selelkula on 27 August (coded separately). The protesters chanted slogans calling for the government to ensure accountability and condemned its failure to protect civilians.</t>
+        </is>
+      </c>
+      <c r="BJ34" t="inlineStr">
+        <is>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="BK34" t="inlineStr">
+        <is>
+          <t>Buno Bedele</t>
+        </is>
+      </c>
+      <c r="BL34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ET0417</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ET0412</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ET0203;ET0206;ET0409;ET0411;ET0412;ET0417;ET1602;ET1603;ET1604;ET1605</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>88.79922123147091</v>
+      </c>
+      <c r="I35" t="n">
+        <v>11.20077876852909</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AU35" t="inlineStr"/>
+      <c r="AV35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr"/>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>ET04</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>Abduction/forced disappearance</t>
+        </is>
+      </c>
+      <c r="BE35" t="inlineStr">
+        <is>
+          <t>Police Forces of Ethiopia (2018-) Oromia State Police</t>
+        </is>
+      </c>
+      <c r="BF35" t="inlineStr">
+        <is>
+          <t>Kebele Communal Militia (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG35" t="inlineStr">
+        <is>
+          <t>Civilians (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BI35" t="inlineStr">
+        <is>
+          <t>Around 11 November 2024 (as reported), Oromia regional state police and Kebele militias stopped around 32 civilians, including 15 students between 11 and 16 ages old, and forcefully abducted them in Shashemene town, Shashamane (West Arsi, Oromia). The government forces took them to a detention center with their school uniforms, stating that they were conscripted into the military.</t>
+        </is>
+      </c>
+      <c r="BJ35" t="inlineStr">
+        <is>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="BK35" t="inlineStr">
+        <is>
+          <t>West Arsi</t>
+        </is>
+      </c>
+      <c r="BL35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ET0418</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>ET04</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE36" t="inlineStr">
+        <is>
+          <t>Protesters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF36" t="inlineStr">
+        <is>
+          <t>Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG36" t="inlineStr"/>
+      <c r="BH36" t="inlineStr"/>
+      <c r="BI36" t="inlineStr">
+        <is>
+          <t>On 22 November 2024, ethnic Oromo students protested at Dembi Dolo University, Denbi Dollo town (Kellem Wellega, Oromia), to demand justice for a young man beheaded by suspected Fano militias in Selelkula on 27 August (coded separately). The protesters chanted slogans calling for the government to ensure accountability and condemned its failure to protect civilians.</t>
+        </is>
+      </c>
+      <c r="BJ36" t="inlineStr">
+        <is>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="BK36" t="inlineStr">
+        <is>
+          <t>Kellem Wollega</t>
+        </is>
+      </c>
+      <c r="BL36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ET0419</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr"/>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AU37" t="inlineStr"/>
+      <c r="AV37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr"/>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="AY37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>ET04</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Battles</t>
+        </is>
+      </c>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>Attack ---- Armed clash</t>
+        </is>
+      </c>
+      <c r="BE37" t="inlineStr">
+        <is>
+          <t>Fano Youth Militia ---- Fano Youth Militia</t>
+        </is>
+      </c>
+      <c r="BF37" t="inlineStr"/>
+      <c r="BG37" t="inlineStr">
+        <is>
+          <t>Civilians (Ethiopia) ---- Police Forces of Ethiopia (2018-) Oromia State Police</t>
+        </is>
+      </c>
+      <c r="BH37" t="inlineStr"/>
+      <c r="BI37" t="inlineStr">
+        <is>
+          <t>On 27 July 2024, suspected Fano militias shot and killed 3 civilians (uncorroborated fatalities) in Goda Gefersa kebele (location coded to Tulugana) in Abe Dongoro woreda (Horo Gudru Wellega, Oromia). Several people who fled from the village camped in Tulugana High School. The motive is unknown/not reported. ---- On 9 August 2024, Fano militias clashed with Oromia state police in Charu kebele, Abe Dongoro woreda (Horo Gudru Wellega, Oromia), after Fano attacked and killed civilians (coded separately). At least a member of the Oromia regional police was killed during the clashes. Many civilians were forced to leave and sought shelter in schools in Abe Dongoro due to the insecurity in the area.</t>
+        </is>
+      </c>
+      <c r="BJ37" t="inlineStr">
+        <is>
+          <t>2024-07-27 ---- 2024-08-09</t>
+        </is>
+      </c>
+      <c r="BK37" t="inlineStr">
+        <is>
+          <t>Horo Gudru Wellega</t>
+        </is>
+      </c>
+      <c r="BL37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ET0420</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">July 2024: An unspecified number of educators were among over 300 civilians arrested by Oromia regional police on accusations of being supporters and members of OLF-OLA. </t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>Unspecified Location</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>Police</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>Ethiopian Police</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>Firearms</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>NoInformation</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr"/>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Oromia</t>
+        </is>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>ET04</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr"/>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>Strategic developments</t>
+        </is>
+      </c>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>Arrests</t>
+        </is>
+      </c>
+      <c r="BE38" t="inlineStr">
+        <is>
+          <t>Police Forces of Ethiopia (2018-) Oromia State Police</t>
+        </is>
+      </c>
+      <c r="BF38" t="inlineStr"/>
+      <c r="BG38" t="inlineStr">
+        <is>
+          <t>Civilians (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>Former Military Forces of Ethiopia (2018-); Former Police Forces of Ethiopia (2018-2023) Oromo Regional Special Forces; OLF-OLA: Oromo Liberation Army-Oromo Liberation Front; Teachers (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BI38" t="inlineStr">
+        <is>
+          <t>Around 12 July 2024 (as reported), Oromia regional police arrested over 300 people in Furi 04 kebele, Alem Gena (Sebeta town in the newly formed Shegger City, formerly Finfine Special, Oromia). The detainees included university teachers, former members of the army, and Oromia special forces police suspected of being supporters and members of OLF-OLA.</t>
+        </is>
+      </c>
+      <c r="BJ38" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="BK38" t="inlineStr">
+        <is>
+          <t>Finfine Special</t>
+        </is>
+      </c>
+      <c r="BL38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ET0422</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ET0604</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ET0102;ET0103;ET0106;ET0415;ET0422;ET0604;ET0802</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>59.99360095123959</v>
+      </c>
+      <c r="I39" t="n">
+        <v>36.36756705649405</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.638831992266356</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AU39" t="inlineStr"/>
+      <c r="AV39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr"/>
+      <c r="AX39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr"/>
+      <c r="BA39" t="inlineStr"/>
+      <c r="BB39" t="inlineStr"/>
+      <c r="BC39" t="inlineStr"/>
+      <c r="BD39" t="inlineStr"/>
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="inlineStr"/>
+      <c r="BG39" t="inlineStr"/>
+      <c r="BH39" t="inlineStr"/>
+      <c r="BI39" t="inlineStr"/>
+      <c r="BJ39" t="inlineStr"/>
+      <c r="BK39" t="inlineStr"/>
+      <c r="BL39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ET0502</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="inlineStr"/>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AU40" t="inlineStr"/>
+      <c r="AV40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr"/>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Somali</t>
+        </is>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>ET05</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr"/>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Protest with intervention ---- Protest with intervention</t>
+        </is>
+      </c>
+      <c r="BE40" t="inlineStr">
+        <is>
+          <t>Protesters (Ethiopia) ---- Protesters (Ethiopia) ---- Protesters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF40" t="inlineStr">
+        <is>
+          <t>Oromo Ethnic Group (Ethiopia); Students (Ethiopia) ---- Students (Ethiopia) ---- Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG40" t="inlineStr">
+        <is>
+          <t>Police Forces of Ethiopia (2018-) Somali State Police ---- Police Forces of Ethiopia (2018-) Somali State Police</t>
+        </is>
+      </c>
+      <c r="BH40" t="inlineStr"/>
+      <c r="BI40" t="inlineStr">
+        <is>
+          <t>On 22 November 2024, ethnic Oromo students protested at Jijiga University, Jigjiga town (Fafan, Somali), to demand justice for a young man beheaded by suspected Fano militias in Selelkula on 27 August (coded separately). The protesters chanted slogans calling for the government to ensure accountability and condemned its failure to protect civilians. ---- On 8 April 2025, students of Jigjiga University's graduating class gathered in Jigjiga University (Jijiga, Jigjiga town, Fafan, Somali) for two days (8 and 10 April 2025), demanding an explanation for the cancellation of exit exam results. Somali State Police physically assaulted and dispersed the crowds. The result was cancelled after the students were informed that they had achieved a passing mark in the exam. Ministry of Education claimed that the result was cancelled due to cheating during the examination and notified the students to prepare for a re-examination. Extent of injuries unknown/not reported. ---- On 10 April 2025, for a second day, hundreds of Jigjiga University's graduating class students attempted to gather in Jigjiga University (Jijiga, Jigjiga town, Fafan, Somali), demanding an explanation for the cancellation of exit exam results. Somali State Police physically assaulted and dispersed the gathering. At least 20 students were arrested. The result was canceled after the students were informed that they had achieved a passing mark in the exam. Ministry of Education claimed that the results were cancelled due to cheating during the examination and notified the students to prepare for a re-examination.</t>
+        </is>
+      </c>
+      <c r="BJ40" t="inlineStr">
+        <is>
+          <t>2024-11-22 ---- 2025-04-08 ---- 2025-04-10</t>
+        </is>
+      </c>
+      <c r="BK40" t="inlineStr">
+        <is>
+          <t>Fafan</t>
+        </is>
+      </c>
+      <c r="BL40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ET0507</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AU41" t="inlineStr"/>
+      <c r="AV41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr"/>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Somali</t>
+        </is>
+      </c>
+      <c r="AY41" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>ET05</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr"/>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="BE41" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF41" t="inlineStr"/>
+      <c r="BG41" t="inlineStr">
+        <is>
+          <t>Civilians (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>Muslim Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BI41" t="inlineStr">
+        <is>
+          <t>On 17 September 2024, unidentified gunmen attacked a mosque in Warder town (Warder woreda, Doolo, Somali). The attack is suspected to have a connection with the inter-clan conflicts in the area. 6 youths (five from the same family) were killed. The victims were Islamic students who were preparing for a prayer at the mosque. Government security forces were deployed to the area after the incident.</t>
+        </is>
+      </c>
+      <c r="BJ41" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="BK41" t="inlineStr">
+        <is>
+          <t>Doolo</t>
+        </is>
+      </c>
+      <c r="BL41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ET0602</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="n">
+        <v>1</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>March 2025: An education facility was hit by an airstrike from ENDF forces.</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building </t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>Ethiopian National Defense Forces</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>Aerial Bomb: Plane</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr">
+        <is>
+          <t>School: No Further Details</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr"/>
+      <c r="AV42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr"/>
+      <c r="AX42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr"/>
+      <c r="BA42" t="inlineStr"/>
+      <c r="BB42" t="inlineStr"/>
+      <c r="BC42" t="inlineStr"/>
+      <c r="BD42" t="inlineStr"/>
+      <c r="BE42" t="inlineStr"/>
+      <c r="BF42" t="inlineStr"/>
+      <c r="BG42" t="inlineStr"/>
+      <c r="BH42" t="inlineStr"/>
+      <c r="BI42" t="inlineStr"/>
+      <c r="BJ42" t="inlineStr"/>
+      <c r="BK42" t="inlineStr"/>
+      <c r="BL42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ET0603</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
+      <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AU43" t="inlineStr"/>
+      <c r="AV43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr"/>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Benshangul/Gumuz</t>
+        </is>
+      </c>
+      <c r="AY43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>ET06</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr"/>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE43" t="inlineStr">
+        <is>
+          <t>Protesters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF43" t="inlineStr">
+        <is>
+          <t>Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG43" t="inlineStr"/>
+      <c r="BH43" t="inlineStr"/>
+      <c r="BI43" t="inlineStr">
+        <is>
+          <t>On 21 November 2024, ethnic Oromo university students protested at Asosa University (Assosa, Benshangul/Gumuz), demanding justice and accountability for the ethnic Oromo youth killed (beheaded) by Fano in Selelkula on 27 August (coded separately).</t>
+        </is>
+      </c>
+      <c r="BJ43" t="inlineStr">
+        <is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="BK43" t="inlineStr">
+        <is>
+          <t>Asosa</t>
+        </is>
+      </c>
+      <c r="BL43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ET0604</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ET0422</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ET0102;ET0103;ET0106;ET0415;ET0422;ET0604;ET0802</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>56.37706578854814</v>
+      </c>
+      <c r="I44" t="n">
+        <v>42.82191582723836</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.8010183842135069</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
+      <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="inlineStr"/>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AU44" t="inlineStr"/>
+      <c r="AV44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr"/>
+      <c r="AX44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr"/>
+      <c r="BA44" t="inlineStr"/>
+      <c r="BB44" t="inlineStr"/>
+      <c r="BC44" t="inlineStr"/>
+      <c r="BD44" t="inlineStr"/>
+      <c r="BE44" t="inlineStr"/>
+      <c r="BF44" t="inlineStr"/>
+      <c r="BG44" t="inlineStr"/>
+      <c r="BH44" t="inlineStr"/>
+      <c r="BI44" t="inlineStr"/>
+      <c r="BJ44" t="inlineStr"/>
+      <c r="BK44" t="inlineStr"/>
+      <c r="BL44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ET0702</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AU45" t="inlineStr"/>
+      <c r="AV45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr"/>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Central Ethiopia</t>
+        </is>
+      </c>
+      <c r="AY45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>ET07</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr"/>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE45" t="inlineStr">
+        <is>
+          <t>Protesters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF45" t="inlineStr">
+        <is>
+          <t>Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG45" t="inlineStr"/>
+      <c r="BH45" t="inlineStr"/>
+      <c r="BI45" t="inlineStr">
+        <is>
+          <t>On 22 November 2024, ethnic Oromo university students staged a peaceful demonstration at Wachemo University (Lemmo, Hadiya, Central Ethiopia), demanding justice and accountability for the ethnic Oromo youth killed (beheaded) by suspected Fano members in Selelkula on 27 August (coded separately).</t>
+        </is>
+      </c>
+      <c r="BJ45" t="inlineStr">
+        <is>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="BK45" t="inlineStr">
+        <is>
+          <t>Hadiya</t>
+        </is>
+      </c>
+      <c r="BL45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ET0706</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="n">
+        <v>1</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN46" t="inlineStr">
+        <is>
+          <t>2024-10-27 ---- 2024-10-12</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>As reported in October 2024: An unspecified number of educators were arrested by police for submitting petitions about overdue salaries, accusing them of inciting violence and damaging the administration's reputation. ---- October 2024: An educational facility was hit by ENDF airstrikes, killing four people.</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unspecified Location ---- Education Building </t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>Police ---- Other</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>Ethiopian Police ---- Ethiopian National Defense Forces</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>No Information on the Weapon Used ---- Aerial Bomb: Plane</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr">
+        <is>
+          <t>Not Applicable ---- Primary School</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>NoInformation</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr"/>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>South Ethiopia Region</t>
+        </is>
+      </c>
+      <c r="AY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>ET07</t>
+        </is>
+      </c>
+      <c r="BB46" t="inlineStr"/>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>Strategic developments ---- Strategic developments</t>
+        </is>
+      </c>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>Arrests ---- Arrests</t>
+        </is>
+      </c>
+      <c r="BE46" t="inlineStr">
+        <is>
+          <t>Police Forces of Ethiopia (2023-) South Ethiopia State Police ---- Police Forces of Ethiopia (2023-) South Ethiopia State Police</t>
+        </is>
+      </c>
+      <c r="BF46" t="inlineStr"/>
+      <c r="BG46" t="inlineStr">
+        <is>
+          <t>Civilians (Ethiopia) ---- Civilians (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BH46" t="inlineStr">
+        <is>
+          <t>Teachers (Ethiopia) ---- Lawyers (Ethiopia); Teachers (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BI46" t="inlineStr">
+        <is>
+          <t>Around 23 October 2024 (week of), South Ethiopia state police arrested several teachers from across the Welayta zone (location coded to the admin center, Sodo Town, Sodo, Welayta, South Ethiopia Region) after they collected petitions demanding the payment of their overdue salaries. The police accused them of inciting violence and damaging the reputation of the Zonal administration. ---- Around 21 March 2025 (as reported), South Ethiopia state police arrested an unspecified number of civilians (including university lecturers and lawyers/advocates) in Sodo (Sodo Town, Welayta, South Ethiopia Region). The families of the victims complained that the police arrested the victims en masse through house-to-hose searches and from roads, accusing the victims of criticizing the leadership of the region on social media. The Welayta zone justice bureau head, on the other hand, stated that the victims were arrested because of their participation in hate speech. The victims' families further criticized the arrest for failing to respect the victims' due process rights, and the arrest was conducted by disregarding the legal and constitutional processes.</t>
+        </is>
+      </c>
+      <c r="BJ46" t="inlineStr">
+        <is>
+          <t>2024-10-23 ---- 2025-03-21</t>
+        </is>
+      </c>
+      <c r="BK46" t="inlineStr">
+        <is>
+          <t>Welayta</t>
+        </is>
+      </c>
+      <c r="BL46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ET0710</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr"/>
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AU47" t="inlineStr"/>
+      <c r="AV47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr"/>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>South Ethiopia Region</t>
+        </is>
+      </c>
+      <c r="AY47" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>ET07</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr"/>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="BE47" t="inlineStr">
+        <is>
+          <t>Police Forces of Ethiopia (2023-) South Ethiopia State Police</t>
+        </is>
+      </c>
+      <c r="BF47" t="inlineStr">
+        <is>
+          <t>Kebele Communal Militia (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG47" t="inlineStr">
+        <is>
+          <t>Civilians (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BH47" t="inlineStr"/>
+      <c r="BI47" t="inlineStr">
+        <is>
+          <t>On 7 June 2024, security forces (likely South State police and Kebele militia based on their previous involvement in similar incidents) opened fire at civilians at Mayile Sefer, Zense Sefer, Awusha school, and at another unspecified location in Zeyse Dambile Kebele in Arba Minch Zuria Woreda (locations coded to the admin center of the woreda, Arba Minch, Arba Minch town, Gamo, South Ethiopia). The attack erupted in relation to a renewed demand for the liyu woreda structure by the Zeyse community. At least 5 civilians were killed.</t>
+        </is>
+      </c>
+      <c r="BJ47" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="BK47" t="inlineStr">
+        <is>
+          <t>Gamo</t>
+        </is>
+      </c>
+      <c r="BL47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ET0720</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr"/>
+      <c r="AQ48" t="inlineStr"/>
+      <c r="AR48" t="inlineStr"/>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AU48" t="inlineStr"/>
+      <c r="AV48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr"/>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Central Ethiopia</t>
+        </is>
+      </c>
+      <c r="AY48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>ET07</t>
+        </is>
+      </c>
+      <c r="BB48" t="inlineStr"/>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE48" t="inlineStr">
+        <is>
+          <t>Protesters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF48" t="inlineStr">
+        <is>
+          <t>Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG48" t="inlineStr"/>
+      <c r="BH48" t="inlineStr"/>
+      <c r="BI48" t="inlineStr">
+        <is>
+          <t>On 22 November 2024, ethnic Oromo university students protested at Worabe University (Siltie, Worabe town, Central Ethiopia), demanding justice and accountability for the ethnic Oromo youth killed (beheaded) by Fano in Selelkula on 27 August (coded separately).</t>
+        </is>
+      </c>
+      <c r="BJ48" t="inlineStr">
+        <is>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="BK48" t="inlineStr">
+        <is>
+          <t>Siltie</t>
+        </is>
+      </c>
+      <c r="BL48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ET0721</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="inlineStr"/>
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="inlineStr"/>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AU49" t="inlineStr"/>
+      <c r="AV49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr"/>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>South Ethiopia Region</t>
+        </is>
+      </c>
+      <c r="AY49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>ET07</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr"/>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>Strategic developments</t>
+        </is>
+      </c>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>Arrests</t>
+        </is>
+      </c>
+      <c r="BE49" t="inlineStr">
+        <is>
+          <t>Police Forces of Ethiopia (2023-) South Ethiopia State Police</t>
+        </is>
+      </c>
+      <c r="BF49" t="inlineStr"/>
+      <c r="BG49" t="inlineStr">
+        <is>
+          <t>Civilians (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BH49" t="inlineStr">
+        <is>
+          <t>Teachers (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BI49" t="inlineStr">
+        <is>
+          <t>On 21 November 2024, South Ethiopia state police arrested 66 teachers in Derba Menena (Sermale wereda, Amaro, South Ethiopia Region), following their opposition to an unauthorized salary cut by the administration. The Woreda administration claimed that the teachers were arrested for inciting protests. Teaching activities were suspended in 27 schools. The Amaro zone education bureau head stated that the police arrested the teachers because they stopped teaching and threw stones at other teachers during their daily teaching routine.</t>
+        </is>
+      </c>
+      <c r="BJ49" t="inlineStr">
+        <is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="BK49" t="inlineStr">
+        <is>
+          <t>Amaro</t>
+        </is>
+      </c>
+      <c r="BL49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ET0802</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>ET0106</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ET0102;ET0103;ET0106;ET0415;ET0422;ET0604;ET0802</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>96.88832831100149</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2.932561032380277</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.1791106566182307</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O50" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="inlineStr"/>
+      <c r="AQ50" t="inlineStr"/>
+      <c r="AR50" t="inlineStr"/>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AU50" t="inlineStr"/>
+      <c r="AV50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr"/>
+      <c r="AX50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr"/>
+      <c r="BA50" t="inlineStr"/>
+      <c r="BB50" t="inlineStr"/>
+      <c r="BC50" t="inlineStr"/>
+      <c r="BD50" t="inlineStr"/>
+      <c r="BE50" t="inlineStr"/>
+      <c r="BF50" t="inlineStr"/>
+      <c r="BG50" t="inlineStr"/>
+      <c r="BH50" t="inlineStr"/>
+      <c r="BI50" t="inlineStr"/>
+      <c r="BJ50" t="inlineStr"/>
+      <c r="BK50" t="inlineStr"/>
+      <c r="BL50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ET1101</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr"/>
+      <c r="AQ51" t="inlineStr"/>
+      <c r="AR51" t="inlineStr"/>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AU51" t="inlineStr"/>
+      <c r="AV51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr"/>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="AY51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>ET11</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr"/>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE51" t="inlineStr">
+        <is>
+          <t>Protesters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF51" t="inlineStr">
+        <is>
+          <t>Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG51" t="inlineStr"/>
+      <c r="BH51" t="inlineStr"/>
+      <c r="BI51" t="inlineStr">
+        <is>
+          <t>On 21 November 2024, ethnic Oromo university students protested at Mizan Tepi University (Yeki, Sheka, South West), demanding justice and accountability for the ethnic Oromo youth killed (beheaded) by Fano in Selelkula on 27 August (coded separately).</t>
+        </is>
+      </c>
+      <c r="BJ51" t="inlineStr">
+        <is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="BK51" t="inlineStr">
+        <is>
+          <t>Sheka</t>
+        </is>
+      </c>
+      <c r="BL51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ET1102</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
+      <c r="AQ52" t="inlineStr"/>
+      <c r="AR52" t="inlineStr"/>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AU52" t="inlineStr"/>
+      <c r="AV52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr"/>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="AY52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>ET11</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr"/>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE52" t="inlineStr">
+        <is>
+          <t>Protesters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF52" t="inlineStr">
+        <is>
+          <t>Teachers (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG52" t="inlineStr"/>
+      <c r="BH52" t="inlineStr"/>
+      <c r="BI52" t="inlineStr">
+        <is>
+          <t>On 20 November 2024, around 34 teachers staged a public demonstration in Bonga (Bonga town, Kefa, South West), opposing a deduction of one month's salary from their annual wage. The Wereda cut the demonstrators' salaries for 'alleged development purposes.'</t>
+        </is>
+      </c>
+      <c r="BJ52" t="inlineStr">
+        <is>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+      <c r="BK52" t="inlineStr">
+        <is>
+          <t>Kefa</t>
+        </is>
+      </c>
+      <c r="BL52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ET1201</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr"/>
+      <c r="AQ53" t="inlineStr"/>
+      <c r="AR53" t="inlineStr"/>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AU53" t="inlineStr"/>
+      <c r="AV53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr"/>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Gambela</t>
+        </is>
+      </c>
+      <c r="AY53" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>ET12</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr"/>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="BE53" t="inlineStr">
+        <is>
+          <t>Anyuak Ethnic Militia (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF53" t="inlineStr"/>
+      <c r="BG53" t="inlineStr">
+        <is>
+          <t>Civilians (South Sudan)</t>
+        </is>
+      </c>
+      <c r="BH53" t="inlineStr">
+        <is>
+          <t>Students (South Sudan)</t>
+        </is>
+      </c>
+      <c r="BI53" t="inlineStr">
+        <is>
+          <t>On 21 July 2024, unknown armed assailants (likely ethnic Anyuak militias due to their previous engagement in related violence and the context) attacked and killed at least 5 South Sudanese students and injured four others in an area between Khankan and Gangrial, on the Ethiopian side of South Sudan-Ethiopia border (location coded to Metar) in Wantawo woreda (Nuwer, Gambela). Several others were also missing. The injured were evacuated to Akobo town in South Sudan to receive treatment.</t>
+        </is>
+      </c>
+      <c r="BJ53" t="inlineStr">
+        <is>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="BK53" t="inlineStr">
+        <is>
+          <t>Nuwer</t>
+        </is>
+      </c>
+      <c r="BL53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ET1202</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr"/>
+      <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
+      <c r="AP54" t="inlineStr"/>
+      <c r="AQ54" t="inlineStr"/>
+      <c r="AR54" t="inlineStr"/>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AU54" t="inlineStr"/>
+      <c r="AV54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr"/>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Gambela</t>
+        </is>
+      </c>
+      <c r="AY54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>ET12</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr"/>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="BE54" t="inlineStr">
+        <is>
+          <t>Murle Ethnic Militia (South Sudan)</t>
+        </is>
+      </c>
+      <c r="BF54" t="inlineStr"/>
+      <c r="BG54" t="inlineStr">
+        <is>
+          <t>Civilians (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BH54" t="inlineStr">
+        <is>
+          <t>Students (Ethiopia); Women (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BI54" t="inlineStr">
+        <is>
+          <t>On 25 June 2025, Murle ethnic militia from South Sudan opened fire and abducted 4 girls (aged 13-22) while they were traveling from Taada Kebele to Pugnido town (coded to Taada, Gog, Agnewak, Gambela). Motivation unknown. Three of the abductees were students who were traveling to Pugnido to sit for the 12th-grade national exam. The regional police commission deployed police forces to rescue the girls.</t>
+        </is>
+      </c>
+      <c r="BJ54" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="BK54" t="inlineStr">
+        <is>
+          <t>Agnewak</t>
+        </is>
+      </c>
+      <c r="BL54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ET1401</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
+      <c r="AP55" t="inlineStr"/>
+      <c r="AQ55" t="inlineStr"/>
+      <c r="AR55" t="inlineStr"/>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AU55" t="inlineStr"/>
+      <c r="AV55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr"/>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="AY55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>ET14</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr"/>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>Abduction/forced disappearance ---- Protest with intervention ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE55" t="inlineStr">
+        <is>
+          <t>Police Forces of Ethiopia (2018-) Oromia State Police ---- Protesters (Ethiopia) ---- Protesters (Ethiopia) ---- Protesters (Ethiopia) ---- Protesters (Ethiopia) ---- Protesters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF55" t="inlineStr">
+        <is>
+          <t>Students (Ethiopia) ---- Oromo Ethnic Group (Ethiopia); Students (Ethiopia) ---- Oromo Ethnic Group (Ethiopia); Students (Ethiopia) ---- Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG55" t="inlineStr">
+        <is>
+          <t>Civilians (Ethiopia) ---- Police Forces of Ethiopia (2018-) Federal Police</t>
+        </is>
+      </c>
+      <c r="BH55" t="inlineStr">
+        <is>
+          <t>Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BI55" t="inlineStr">
+        <is>
+          <t>On 10 March 2024, an unidentified armed group (likely Oromia Regional state police, due to the location of the incident) kidnapped a university student after stopping a minibus without a plate in front of Oromia regional state police commission in Sidist Kilo, Gullele/Gulele sub-city (Region 14, Addis Ababa). Families were unable to identify the whereabouts of the abductee. Motivation unknown/not reported. ---- On 10 April 2024, students of Addis Ababa University in Sidist Kilo staged a protest in Sidist Kilo Campus, Gulele, Addis Ababa (Region 14, Addis Ababa) to condemn the killing of an OLF politician by an unknown armed group (coded separately). The government security forces (coded as Federal Police) intervened (means not mentioned/specified) and dispersed the protesters. ---- On 29 July 2024, parents of students protested in the Addis Global School (private) compound in Bole (Region 14, Addis Ababa), opposing the planned demolishment of the school building for the government's corridor development project. The parents complained that the demolishment plan was notified after the registration for the 2017 Ethiopian academic year was completed, and they could not register their children in other schools. ---- On 21 November 2024, ethnic Oromo students staged a protest at Addis Ababa University, Gulele (Region 14, Addis Ababa), to demand justice for a young man beheaded by suspected Fano militias in Selelkula on 27 August (coded separately). The protesters chanted slogans calling for the government to ensure accountability and condemned its failure to protect civilians. ---- On 21 November 2024, ethnic Oromo students staged a protest at Kotobe University, Yeka sub-city (Region 14, Addis Ababa), to demand justice for a young man beheaded by suspected Fano militias in Selelkula on 27 August (coded separately). The protesters chanted slogans calling for the government to ensure accountability and protect civilians from violence. ---- On 22 November 2024, and for a second day, ethnic Oromo students staged a protest at Addis Ababa University, Gulele (Region 14, Addis Ababa), to demand justice for a young man beheaded by suspected Fano militias in Selelkula on 27 August (coded separately). The protesters chanted slogans calling for the government to ensure accountability and condemned its failure to protect civilians.</t>
+        </is>
+      </c>
+      <c r="BJ55" t="inlineStr">
+        <is>
+          <t>2024-03-10 ---- 2024-04-10 ---- 2024-07-29 ---- 2024-11-21 ---- 2024-11-21 ---- 2024-11-22</t>
+        </is>
+      </c>
+      <c r="BK55" t="inlineStr">
+        <is>
+          <t>Region 14</t>
+        </is>
+      </c>
+      <c r="BL55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ET1501</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
+      <c r="AP56" t="inlineStr"/>
+      <c r="AQ56" t="inlineStr"/>
+      <c r="AR56" t="inlineStr"/>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AU56" t="inlineStr"/>
+      <c r="AV56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr"/>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Dire Dawa</t>
+        </is>
+      </c>
+      <c r="AY56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>ET15</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr"/>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE56" t="inlineStr">
+        <is>
+          <t>Protesters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF56" t="inlineStr">
+        <is>
+          <t>Oromo Ethnic Group (Ethiopia); Students (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG56" t="inlineStr"/>
+      <c r="BH56" t="inlineStr"/>
+      <c r="BI56" t="inlineStr">
+        <is>
+          <t>On 21 November 2024, ethnic Oromo students staged a protest at Dire Dawa University, Gende Kore (Dire Dawa, Dire Dawa), to demand justice for a young man beheaded by suspected Fano militias in Selelkula on 27 August (coded separately). The protesters chanted slogans calling for the government to ensure accountability and protect civilians from violence.</t>
+        </is>
+      </c>
+      <c r="BJ56" t="inlineStr">
+        <is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="BK56" t="inlineStr">
+        <is>
+          <t>Dire Dawa urban</t>
+        </is>
+      </c>
+      <c r="BL56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ET1600</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr"/>
+      <c r="AJ57" t="inlineStr"/>
+      <c r="AK57" t="inlineStr"/>
+      <c r="AL57" t="inlineStr"/>
+      <c r="AM57" t="inlineStr"/>
+      <c r="AN57" t="inlineStr"/>
+      <c r="AO57" t="inlineStr"/>
+      <c r="AP57" t="inlineStr"/>
+      <c r="AQ57" t="inlineStr"/>
+      <c r="AR57" t="inlineStr"/>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AU57" t="inlineStr"/>
+      <c r="AV57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr"/>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Sidama</t>
+        </is>
+      </c>
+      <c r="AY57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>ET16</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr"/>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>Protest with intervention</t>
+        </is>
+      </c>
+      <c r="BE57" t="inlineStr">
+        <is>
+          <t>Protesters (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BF57" t="inlineStr">
+        <is>
+          <t>Teachers (Ethiopia)</t>
+        </is>
+      </c>
+      <c r="BG57" t="inlineStr">
+        <is>
+          <t>Police Forces of Ethiopia (2021-) Sidama State Police</t>
+        </is>
+      </c>
+      <c r="BH57" t="inlineStr"/>
+      <c r="BI57" t="inlineStr">
+        <is>
+          <t>On 16 December 2024, a group of teachers from Teticha wereda staged a peaceful demonstration in Teticha (Sidama), opposing their salary deduction (amount unknown/not reported) for the Prosperity Party's fifth-year anniversary celebration. The Sidama state police assaulted the protesters (means unknown/not reported) and arrested an unspecified number of teachers.</t>
+        </is>
+      </c>
+      <c r="BJ57" t="inlineStr">
+        <is>
+          <t>2024-12-16</t>
+        </is>
+      </c>
+      <c r="BK57" t="inlineStr">
+        <is>
+          <t>Sidama</t>
+        </is>
+      </c>
+      <c r="BL57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ET1601</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>ET1601</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ET1601</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>91.74523834390045</v>
+      </c>
+      <c r="I58" t="n">
+        <v>8.254761656099554</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr"/>
+      <c r="AJ58" t="inlineStr"/>
+      <c r="AK58" t="inlineStr"/>
+      <c r="AL58" t="inlineStr"/>
+      <c r="AM58" t="inlineStr"/>
+      <c r="AN58" t="inlineStr"/>
+      <c r="AO58" t="inlineStr"/>
+      <c r="AP58" t="inlineStr"/>
+      <c r="AQ58" t="inlineStr"/>
+      <c r="AR58" t="inlineStr"/>
+      <c r="AS58" t="inlineStr"/>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AU58" t="inlineStr"/>
+      <c r="AV58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr"/>
+      <c r="AX58" t="inlineStr"/>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr"/>
+      <c r="BA58" t="inlineStr"/>
+      <c r="BB58" t="inlineStr"/>
+      <c r="BC58" t="inlineStr"/>
+      <c r="BD58" t="inlineStr"/>
+      <c r="BE58" t="inlineStr"/>
+      <c r="BF58" t="inlineStr"/>
+      <c r="BG58" t="inlineStr"/>
+      <c r="BH58" t="inlineStr"/>
+      <c r="BI58" t="inlineStr"/>
+      <c r="BJ58" t="inlineStr"/>
+      <c r="BK58" t="inlineStr"/>
+      <c r="BL58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ET1602</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>ET1604</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ET0203;ET0206;ET0409;ET0411;ET0412;ET0417;ET1602;ET1603;ET1604;ET1605</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>98.60079548273832</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1.399204517261678</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="O59" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr"/>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr"/>
+      <c r="AJ59" t="inlineStr"/>
+      <c r="AK59" t="inlineStr"/>
+      <c r="AL59" t="inlineStr"/>
+      <c r="AM59" t="inlineStr"/>
+      <c r="AN59" t="inlineStr"/>
+      <c r="AO59" t="inlineStr"/>
+      <c r="AP59" t="inlineStr"/>
+      <c r="AQ59" t="inlineStr"/>
+      <c r="AR59" t="inlineStr"/>
+      <c r="AS59" t="inlineStr"/>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AU59" t="inlineStr"/>
+      <c r="AV59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr"/>
+      <c r="AX59" t="inlineStr"/>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr"/>
+      <c r="BA59" t="inlineStr"/>
+      <c r="BB59" t="inlineStr"/>
+      <c r="BC59" t="inlineStr"/>
+      <c r="BD59" t="inlineStr"/>
+      <c r="BE59" t="inlineStr"/>
+      <c r="BF59" t="inlineStr"/>
+      <c r="BG59" t="inlineStr"/>
+      <c r="BH59" t="inlineStr"/>
+      <c r="BI59" t="inlineStr"/>
+      <c r="BJ59" t="inlineStr"/>
+      <c r="BK59" t="inlineStr"/>
+      <c r="BL59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ET1603</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>ET0203</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>ET0203;ET0206;ET0409;ET0411;ET0412;ET0417;ET1602;ET1603;ET1604;ET1605</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>98.56841068818423</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.431589311815775</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr"/>
+      <c r="AJ60" t="inlineStr"/>
+      <c r="AK60" t="inlineStr"/>
+      <c r="AL60" t="inlineStr"/>
+      <c r="AM60" t="inlineStr"/>
+      <c r="AN60" t="inlineStr"/>
+      <c r="AO60" t="inlineStr"/>
+      <c r="AP60" t="inlineStr"/>
+      <c r="AQ60" t="inlineStr"/>
+      <c r="AR60" t="inlineStr"/>
+      <c r="AS60" t="inlineStr"/>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AU60" t="inlineStr"/>
+      <c r="AV60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr"/>
+      <c r="AX60" t="inlineStr"/>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr"/>
+      <c r="BA60" t="inlineStr"/>
+      <c r="BB60" t="inlineStr"/>
+      <c r="BC60" t="inlineStr"/>
+      <c r="BD60" t="inlineStr"/>
+      <c r="BE60" t="inlineStr"/>
+      <c r="BF60" t="inlineStr"/>
+      <c r="BG60" t="inlineStr"/>
+      <c r="BH60" t="inlineStr"/>
+      <c r="BI60" t="inlineStr"/>
+      <c r="BJ60" t="inlineStr"/>
+      <c r="BK60" t="inlineStr"/>
+      <c r="BL60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ET1604</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>ET1602</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ET0203;ET0206;ET0409;ET0411;ET0412;ET0417;ET1602;ET1603;ET1604;ET1605</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>96.36249574924338</v>
+      </c>
+      <c r="I61" t="n">
+        <v>3.637504250756623</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="inlineStr"/>
+      <c r="AN61" t="inlineStr"/>
+      <c r="AO61" t="inlineStr"/>
+      <c r="AP61" t="inlineStr"/>
+      <c r="AQ61" t="inlineStr"/>
+      <c r="AR61" t="inlineStr"/>
+      <c r="AS61" t="inlineStr"/>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AU61" t="inlineStr"/>
+      <c r="AV61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr"/>
+      <c r="AX61" t="inlineStr"/>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr"/>
+      <c r="BA61" t="inlineStr"/>
+      <c r="BB61" t="inlineStr"/>
+      <c r="BC61" t="inlineStr"/>
+      <c r="BD61" t="inlineStr"/>
+      <c r="BE61" t="inlineStr"/>
+      <c r="BF61" t="inlineStr"/>
+      <c r="BG61" t="inlineStr"/>
+      <c r="BH61" t="inlineStr"/>
+      <c r="BI61" t="inlineStr"/>
+      <c r="BJ61" t="inlineStr"/>
+      <c r="BK61" t="inlineStr"/>
+      <c r="BL61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ET1605</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>ET1602</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>ET0203;ET0206;ET0409;ET0411;ET0412;ET0417;ET1602;ET1603;ET1604;ET1605</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>94.10772236368</v>
+      </c>
+      <c r="I62" t="n">
+        <v>5.89227763632001</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="inlineStr"/>
+      <c r="AN62" t="inlineStr"/>
+      <c r="AO62" t="inlineStr"/>
+      <c r="AP62" t="inlineStr"/>
+      <c r="AQ62" t="inlineStr"/>
+      <c r="AR62" t="inlineStr"/>
+      <c r="AS62" t="inlineStr"/>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AU62" t="inlineStr"/>
+      <c r="AV62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr"/>
+      <c r="AX62" t="inlineStr"/>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr"/>
+      <c r="BA62" t="inlineStr"/>
+      <c r="BB62" t="inlineStr"/>
+      <c r="BC62" t="inlineStr"/>
+      <c r="BD62" t="inlineStr"/>
+      <c r="BE62" t="inlineStr"/>
+      <c r="BF62" t="inlineStr"/>
+      <c r="BG62" t="inlineStr"/>
+      <c r="BH62" t="inlineStr"/>
+      <c r="BI62" t="inlineStr"/>
+      <c r="BJ62" t="inlineStr"/>
+      <c r="BK62" t="inlineStr"/>
+      <c r="BL62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3363,13 +9085,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{629AD787-CA44-42FF-A0A9-FD41C30150BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FB14D38-0127-4340-96D2-DB7907E74771}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87B0247E-724B-4603-90E9-1A3D7D4E3E22}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCCB4477-64D4-408F-A3E5-4A8796229C7C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2128B7A-A2EC-4FD4-88DD-B61EA906DB78}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F0AB549-B43B-4287-A4D9-8D9400AB94B9}"/>
 </file>